--- a/MISSION/CAMPAÑA/DOCS/ECONOMIA CAMPAÑA.xlsx
+++ b/MISSION/CAMPAÑA/DOCS/ECONOMIA CAMPAÑA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Saved Games\DCS.openbeta\Missions\GITHUB\MISSION\CAMPAÑA\DOCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{090C46F0-4C50-4C22-9EDE-501C979E2F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC32F308-6F47-4E9D-A879-B8B97446E98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-195" yWindow="-16320" windowWidth="38640" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aviones" sheetId="8" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="257">
   <si>
     <t>PL-5EII</t>
   </si>
@@ -641,9 +641,6 @@
     <t>Señuelo</t>
   </si>
   <si>
-    <t>Harppon</t>
-  </si>
-  <si>
     <t>LD-10</t>
   </si>
   <si>
@@ -792,6 +789,33 @@
   </si>
   <si>
     <t>SEÑUELOS</t>
+  </si>
+  <si>
+    <t>SUIZA</t>
+  </si>
+  <si>
+    <t>RB-24 (AIM-9B) Sidewinder IR AAM</t>
+  </si>
+  <si>
+    <t>RB-24J (AIM-9P3) Sidewinder IR AAM</t>
+  </si>
+  <si>
+    <t>UnGd Rkts, 68 mm SNEB Type 253 F1B HEAT</t>
+  </si>
+  <si>
+    <t>AntiShip</t>
+  </si>
+  <si>
+    <t>M/71 HE-Bomb W Chute</t>
+  </si>
+  <si>
+    <t>M/71 HE-Bomb</t>
+  </si>
+  <si>
+    <t>BK90 MJ1 - MJ2</t>
+  </si>
+  <si>
+    <t>RB-15F</t>
   </si>
 </sst>
 </file>
@@ -907,7 +931,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -968,6 +992,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="72">
     <border>
@@ -1870,7 +1900,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="291">
+  <cellXfs count="319">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2170,9 +2200,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2300,9 +2327,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2327,19 +2351,10 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -2393,16 +2408,31 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2438,12 +2468,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2489,12 +2513,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2540,28 +2558,31 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2571,9 +2592,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2639,29 +2657,117 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="56" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2998,12 +3104,12 @@
       <c r="A1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="200" t="s">
+      <c r="B1" s="202" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="201"/>
+      <c r="C1" s="202"/>
+      <c r="D1" s="202"/>
+      <c r="E1" s="203"/>
       <c r="F1" s="9" t="s">
         <v>39</v>
       </c>
@@ -3019,13 +3125,13 @@
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
-      <c r="B2" s="171"/>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
-      <c r="F2" s="171"/>
-      <c r="G2" s="175"/>
-      <c r="H2" s="171"/>
+      <c r="B2" s="169"/>
+      <c r="C2" s="169"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="173"/>
+      <c r="H2" s="169"/>
       <c r="I2" s="15"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3865,7 +3971,7 @@
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="60" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B35" s="47">
         <v>1</v>
@@ -3895,7 +4001,7 @@
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="60" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B36" s="47">
         <v>1</v>
@@ -3925,7 +4031,7 @@
     </row>
     <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="60" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B37" s="47">
         <v>1</v>
@@ -3961,7 +4067,7 @@
       <c r="E38"/>
       <c r="F38"/>
       <c r="G38"/>
-      <c r="K38" s="122"/>
+      <c r="K38" s="121"/>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="60" t="s">
@@ -4255,14 +4361,15 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="50" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="2.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="29.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.28515625" style="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.140625" customWidth="1"/>
@@ -4277,12 +4384,12 @@
       <c r="C1" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="182" t="s">
+      <c r="D1" s="177" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="183"/>
-      <c r="F1" s="183"/>
-      <c r="G1" s="184"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="179"/>
       <c r="H1" s="15" t="s">
         <v>39</v>
       </c>
@@ -4529,11 +4636,11 @@
         <v>120000</v>
       </c>
       <c r="J8" s="71">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K8" s="68">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2400000</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -4563,11 +4670,11 @@
         <v>130000</v>
       </c>
       <c r="J9" s="71">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K9" s="68">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1300000</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -4631,11 +4738,11 @@
         <v>325000</v>
       </c>
       <c r="J11" s="71">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K11" s="68">
         <f t="shared" si="0"/>
-        <v>3250000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -4661,7 +4768,7 @@
       <c r="H12" s="75">
         <v>1259</v>
       </c>
-      <c r="I12" s="185">
+      <c r="I12" s="180">
         <v>10000</v>
       </c>
       <c r="J12" s="71">
@@ -4974,7 +5081,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="68">
-        <f t="shared" ref="K21:K53" si="2">I21*J21</f>
+        <f t="shared" ref="K21:K55" si="2">I21*J21</f>
         <v>0</v>
       </c>
     </row>
@@ -5727,11 +5834,11 @@
         <v>80000</v>
       </c>
       <c r="J44" s="71">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K44" s="68">
         <f t="shared" si="2"/>
-        <v>800000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -5829,11 +5936,11 @@
         <v>76000</v>
       </c>
       <c r="J47" s="71">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K47" s="68">
         <f t="shared" si="2"/>
-        <v>1520000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -5897,11 +6004,11 @@
         <v>110000</v>
       </c>
       <c r="J49" s="71">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K49" s="68">
         <f t="shared" si="2"/>
-        <v>1100000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -5939,7 +6046,7 @@
       </c>
     </row>
     <row r="51" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="202" t="s">
+      <c r="A51" s="278" t="s">
         <v>100</v>
       </c>
       <c r="B51" s="117" t="s">
@@ -5975,7 +6082,7 @@
       </c>
     </row>
     <row r="52" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="203"/>
+      <c r="A52" s="279"/>
       <c r="B52" s="105" t="s">
         <v>99</v>
       </c>
@@ -6009,62 +6116,134 @@
       </c>
     </row>
     <row r="53" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="203"/>
-      <c r="B53" s="106" t="s">
+      <c r="A53" s="280"/>
+      <c r="B53" s="283" t="s">
         <v>101</v>
       </c>
-      <c r="C53" s="88">
+      <c r="C53" s="287">
         <v>2</v>
       </c>
-      <c r="D53" s="27">
-        <v>4</v>
-      </c>
-      <c r="E53" s="19">
-        <v>4</v>
-      </c>
-      <c r="F53" s="19">
+      <c r="D53" s="34">
+        <v>4</v>
+      </c>
+      <c r="E53" s="17">
+        <v>4</v>
+      </c>
+      <c r="F53" s="17">
         <v>34</v>
       </c>
-      <c r="G53" s="28">
+      <c r="G53" s="288">
         <v>291</v>
       </c>
-      <c r="H53" s="76">
+      <c r="H53" s="289">
         <v>1300</v>
       </c>
-      <c r="I53" s="92">
+      <c r="I53" s="290">
         <v>65000</v>
       </c>
-      <c r="J53" s="72">
-        <v>0</v>
-      </c>
-      <c r="K53" s="73">
+      <c r="J53" s="141">
+        <v>0</v>
+      </c>
+      <c r="K53" s="69">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I54" s="176" t="s">
+    <row r="54" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="281" t="s">
+        <v>248</v>
+      </c>
+      <c r="B54" s="286" t="s">
+        <v>249</v>
+      </c>
+      <c r="C54" s="35">
+        <v>2</v>
+      </c>
+      <c r="D54" s="23">
+        <v>4</v>
+      </c>
+      <c r="E54" s="18">
+        <v>4</v>
+      </c>
+      <c r="F54" s="18">
+        <v>7</v>
+      </c>
+      <c r="G54" s="24">
+        <v>11037</v>
+      </c>
+      <c r="H54" s="35">
+        <v>1301</v>
+      </c>
+      <c r="I54" s="52">
+        <v>27000</v>
+      </c>
+      <c r="J54" s="70">
+        <v>0</v>
+      </c>
+      <c r="K54" s="52">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="282"/>
+      <c r="B55" s="286" t="s">
+        <v>250</v>
+      </c>
+      <c r="C55" s="38">
+        <v>2</v>
+      </c>
+      <c r="D55" s="27">
+        <v>4</v>
+      </c>
+      <c r="E55" s="19">
+        <v>4</v>
+      </c>
+      <c r="F55" s="19">
+        <v>7</v>
+      </c>
+      <c r="G55" s="28">
+        <v>11038</v>
+      </c>
+      <c r="H55" s="38">
+        <v>1302</v>
+      </c>
+      <c r="I55" s="55">
+        <v>110000</v>
+      </c>
+      <c r="J55" s="72">
+        <v>10</v>
+      </c>
+      <c r="K55" s="55">
+        <f t="shared" si="2"/>
+        <v>1100000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H56" s="194"/>
+      <c r="I56" s="291" t="s">
         <v>43</v>
       </c>
-      <c r="J54" s="177"/>
-      <c r="K54" s="180">
-        <f>SUM(K2:K53)</f>
-        <v>6670000</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I55" s="178"/>
-      <c r="J55" s="179"/>
-      <c r="K55" s="181"/>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G56" s="199"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K57" s="161"/>
+      <c r="J56" s="292"/>
+      <c r="K56" s="293">
+        <f>SUM(K2:K55)</f>
+        <v>4800000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I57" s="174"/>
+      <c r="J57" s="175"/>
+      <c r="K57" s="176"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G58" s="194"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K59" s="160"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="A54:A55"/>
     <mergeCell ref="A51:A53"/>
     <mergeCell ref="A25:A40"/>
     <mergeCell ref="A41:A42"/>
@@ -6081,7 +6260,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="76.7109375" style="5" customWidth="1"/>
@@ -6094,19 +6273,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="125"/>
+      <c r="A1" s="124"/>
       <c r="B1" s="14" t="s">
         <v>150</v>
       </c>
       <c r="C1" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="D1" s="221" t="s">
+      <c r="D1" s="219" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="222"/>
-      <c r="F1" s="222"/>
-      <c r="G1" s="223"/>
+      <c r="E1" s="220"/>
+      <c r="F1" s="220"/>
+      <c r="G1" s="221"/>
       <c r="H1" s="15"/>
       <c r="I1" s="43" t="s">
         <v>41</v>
@@ -6114,21 +6293,21 @@
       <c r="J1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="123" t="s">
+      <c r="K1" s="122" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="232" t="s">
+      <c r="A2" s="295" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="107" t="s">
-        <v>202</v>
+      <c r="B2" s="62" t="s">
+        <v>201</v>
       </c>
       <c r="C2" s="35" t="s">
         <v>152</v>
       </c>
-      <c r="D2" s="23">
+      <c r="D2" s="125">
         <v>4</v>
       </c>
       <c r="E2" s="18">
@@ -6155,82 +6334,79 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="233"/>
-      <c r="B3" s="105" t="s">
-        <v>203</v>
+      <c r="A3" s="296"/>
+      <c r="B3" s="63" t="s">
+        <v>201</v>
       </c>
       <c r="C3" s="36" t="s">
         <v>152</v>
       </c>
-      <c r="D3" s="25">
-        <v>4</v>
-      </c>
-      <c r="E3" s="2">
+      <c r="D3" s="126">
+        <v>4</v>
+      </c>
+      <c r="E3" s="4">
         <v>5</v>
       </c>
-      <c r="F3" s="2">
-        <v>9</v>
-      </c>
-      <c r="G3" s="3">
-        <v>79</v>
-      </c>
-      <c r="H3" s="36">
-        <v>1251</v>
-      </c>
-      <c r="I3" s="68">
-        <v>2000</v>
-      </c>
-      <c r="J3" s="71">
-        <v>0</v>
-      </c>
-      <c r="K3" s="53">
-        <f t="shared" ref="K3:K54" si="0">I3*J3</f>
+      <c r="F3" s="4">
+        <v>32</v>
+      </c>
+      <c r="G3" s="29">
+        <v>31</v>
+      </c>
+      <c r="H3" s="42"/>
+      <c r="I3" s="94">
+        <v>1200</v>
+      </c>
+      <c r="J3" s="294">
+        <v>0</v>
+      </c>
+      <c r="K3" s="40">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="233"/>
-      <c r="B4" s="105" t="s">
-        <v>153</v>
+      <c r="A4" s="296"/>
+      <c r="B4" s="63" t="s">
+        <v>202</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>159</v>
-      </c>
-      <c r="D4" s="25">
+        <v>152</v>
+      </c>
+      <c r="D4" s="143">
         <v>4</v>
       </c>
       <c r="E4" s="2">
         <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="G4" s="3">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="H4" s="36">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="I4" s="68">
-        <v>22000</v>
+        <v>2000</v>
       </c>
       <c r="J4" s="71">
         <v>0</v>
       </c>
       <c r="K4" s="53">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="K4:K60" si="0">I4*J4</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="233"/>
-      <c r="B5" s="105" t="s">
-        <v>154</v>
+      <c r="A5" s="296"/>
+      <c r="B5" s="63" t="s">
+        <v>153</v>
       </c>
       <c r="C5" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="143">
         <v>4</v>
       </c>
       <c r="E5" s="2">
@@ -6240,13 +6416,13 @@
         <v>36</v>
       </c>
       <c r="G5" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H5" s="36">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="I5" s="68">
-        <v>28000</v>
+        <v>22000</v>
       </c>
       <c r="J5" s="71">
         <v>0</v>
@@ -6257,14 +6433,14 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="233"/>
-      <c r="B6" s="105" t="s">
-        <v>155</v>
+      <c r="A6" s="296"/>
+      <c r="B6" s="63" t="s">
+        <v>154</v>
       </c>
       <c r="C6" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="143">
         <v>4</v>
       </c>
       <c r="E6" s="2">
@@ -6274,13 +6450,13 @@
         <v>36</v>
       </c>
       <c r="G6" s="3">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H6" s="36">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="I6" s="68">
-        <v>65000</v>
+        <v>28000</v>
       </c>
       <c r="J6" s="71">
         <v>0</v>
@@ -6291,14 +6467,14 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="233"/>
-      <c r="B7" s="105" t="s">
-        <v>156</v>
+      <c r="A7" s="296"/>
+      <c r="B7" s="63" t="s">
+        <v>155</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="D7" s="25">
+        <v>159</v>
+      </c>
+      <c r="D7" s="143">
         <v>4</v>
       </c>
       <c r="E7" s="2">
@@ -6308,13 +6484,13 @@
         <v>36</v>
       </c>
       <c r="G7" s="3">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="H7" s="36">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="I7" s="68">
-        <v>60000</v>
+        <v>65000</v>
       </c>
       <c r="J7" s="71">
         <v>0</v>
@@ -6325,14 +6501,14 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="233"/>
-      <c r="B8" s="105" t="s">
-        <v>157</v>
+      <c r="A8" s="296"/>
+      <c r="B8" s="63" t="s">
+        <v>156</v>
       </c>
       <c r="C8" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="143">
         <v>4</v>
       </c>
       <c r="E8" s="2">
@@ -6342,13 +6518,13 @@
         <v>36</v>
       </c>
       <c r="G8" s="3">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H8" s="36">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="I8" s="68">
-        <v>50000</v>
+        <v>60000</v>
       </c>
       <c r="J8" s="71">
         <v>0</v>
@@ -6359,14 +6535,14 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="233"/>
-      <c r="B9" s="105" t="s">
-        <v>206</v>
+      <c r="A9" s="296"/>
+      <c r="B9" s="63" t="s">
+        <v>157</v>
       </c>
       <c r="C9" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="143">
         <v>4</v>
       </c>
       <c r="E9" s="2">
@@ -6376,13 +6552,13 @@
         <v>36</v>
       </c>
       <c r="G9" s="3">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H9" s="36">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="I9" s="68">
-        <v>35000</v>
+        <v>50000</v>
       </c>
       <c r="J9" s="71">
         <v>0</v>
@@ -6393,30 +6569,30 @@
       </c>
     </row>
     <row r="10" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="233"/>
-      <c r="B10" s="105" t="s">
-        <v>158</v>
+      <c r="A10" s="296"/>
+      <c r="B10" s="63" t="s">
+        <v>205</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="D10" s="25">
+        <v>183</v>
+      </c>
+      <c r="D10" s="143">
         <v>4</v>
       </c>
       <c r="E10" s="2">
         <v>5</v>
       </c>
       <c r="F10" s="2">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="G10" s="3">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="H10" s="36">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="I10" s="68">
-        <v>12000</v>
+        <v>35000</v>
       </c>
       <c r="J10" s="71">
         <v>0</v>
@@ -6427,47 +6603,48 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="233"/>
-      <c r="B11" s="105" t="s">
+      <c r="A11" s="296"/>
+      <c r="B11" s="63" t="s">
+        <v>158</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="D11" s="143">
+        <v>4</v>
+      </c>
+      <c r="E11" s="2">
+        <v>5</v>
+      </c>
+      <c r="F11" s="2">
+        <v>7</v>
+      </c>
+      <c r="G11" s="3">
+        <v>62</v>
+      </c>
+      <c r="H11" s="36">
+        <v>1258</v>
+      </c>
+      <c r="I11" s="68">
+        <v>12000</v>
+      </c>
+      <c r="J11" s="71">
+        <v>0</v>
+      </c>
+      <c r="K11" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="296"/>
+      <c r="B12" s="63" t="s">
         <v>160</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="D11" s="25">
-        <v>4</v>
-      </c>
-      <c r="E11" s="2">
-        <v>4</v>
-      </c>
-      <c r="F11" s="2">
-        <v>8</v>
-      </c>
-      <c r="G11" s="3">
-        <v>280</v>
-      </c>
-      <c r="H11" s="36">
-        <v>1259</v>
-      </c>
-      <c r="I11" s="68">
-        <v>900000</v>
-      </c>
-      <c r="J11" s="71">
-        <v>0</v>
-      </c>
-      <c r="K11" s="53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="233"/>
-      <c r="B12" s="105" t="s">
-        <v>161</v>
       </c>
       <c r="C12" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="143">
         <v>4</v>
       </c>
       <c r="E12" s="2">
@@ -6477,13 +6654,13 @@
         <v>8</v>
       </c>
       <c r="G12" s="3">
-        <v>132</v>
+        <v>280</v>
       </c>
       <c r="H12" s="36">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="I12" s="68">
-        <v>1600000</v>
+        <v>900000</v>
       </c>
       <c r="J12" s="71">
         <v>0</v>
@@ -6493,14 +6670,14 @@
       </c>
     </row>
     <row r="13" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="233"/>
-      <c r="B13" s="105" t="s">
-        <v>162</v>
+      <c r="A13" s="296"/>
+      <c r="B13" s="63" t="s">
+        <v>161</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>198</v>
-      </c>
-      <c r="D13" s="25">
+        <v>183</v>
+      </c>
+      <c r="D13" s="143">
         <v>4</v>
       </c>
       <c r="E13" s="2">
@@ -6510,31 +6687,30 @@
         <v>8</v>
       </c>
       <c r="G13" s="3">
-        <v>278</v>
+        <v>132</v>
       </c>
       <c r="H13" s="36">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="I13" s="68">
-        <v>1500000</v>
+        <v>1600000</v>
       </c>
       <c r="J13" s="71">
         <v>0</v>
       </c>
       <c r="K13" s="53">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="233"/>
-      <c r="B14" s="105" t="s">
-        <v>163</v>
+      <c r="A14" s="296"/>
+      <c r="B14" s="63" t="s">
+        <v>162</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="D14" s="25">
+        <v>252</v>
+      </c>
+      <c r="D14" s="143">
         <v>4</v>
       </c>
       <c r="E14" s="2">
@@ -6544,13 +6720,13 @@
         <v>8</v>
       </c>
       <c r="G14" s="3">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H14" s="36">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="I14" s="68">
-        <v>4500000</v>
+        <v>1500000</v>
       </c>
       <c r="J14" s="71">
         <v>0</v>
@@ -6561,14 +6737,14 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="233"/>
-      <c r="B15" s="105" t="s">
-        <v>164</v>
+      <c r="A15" s="296"/>
+      <c r="B15" s="63" t="s">
+        <v>163</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>196</v>
-      </c>
-      <c r="D15" s="25">
+        <v>183</v>
+      </c>
+      <c r="D15" s="143">
         <v>4</v>
       </c>
       <c r="E15" s="2">
@@ -6578,13 +6754,13 @@
         <v>8</v>
       </c>
       <c r="G15" s="3">
-        <v>65</v>
+        <v>279</v>
       </c>
       <c r="H15" s="36">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="I15" s="68">
-        <v>350000</v>
+        <v>4500000</v>
       </c>
       <c r="J15" s="71">
         <v>0</v>
@@ -6595,14 +6771,14 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="233"/>
-      <c r="B16" s="105" t="s">
-        <v>165</v>
+      <c r="A16" s="296"/>
+      <c r="B16" s="63" t="s">
+        <v>164</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>197</v>
-      </c>
-      <c r="D16" s="25">
+        <v>196</v>
+      </c>
+      <c r="D16" s="143">
         <v>4</v>
       </c>
       <c r="E16" s="2">
@@ -6612,13 +6788,13 @@
         <v>8</v>
       </c>
       <c r="G16" s="3">
-        <v>289</v>
+        <v>65</v>
       </c>
       <c r="H16" s="36">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="I16" s="68">
-        <v>20000</v>
+        <v>350000</v>
       </c>
       <c r="J16" s="71">
         <v>0</v>
@@ -6629,14 +6805,14 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="233"/>
-      <c r="B17" s="105" t="s">
-        <v>166</v>
+      <c r="A17" s="296"/>
+      <c r="B17" s="63" t="s">
+        <v>165</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="D17" s="25">
+        <v>197</v>
+      </c>
+      <c r="D17" s="143">
         <v>4</v>
       </c>
       <c r="E17" s="2">
@@ -6646,13 +6822,13 @@
         <v>8</v>
       </c>
       <c r="G17" s="3">
-        <v>77</v>
+        <v>289</v>
       </c>
       <c r="H17" s="36">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="I17" s="68">
-        <v>180000</v>
+        <v>20000</v>
       </c>
       <c r="J17" s="71">
         <v>0</v>
@@ -6663,14 +6839,14 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="233"/>
-      <c r="B18" s="105" t="s">
-        <v>167</v>
+      <c r="A18" s="296"/>
+      <c r="B18" s="63" t="s">
+        <v>166</v>
       </c>
       <c r="C18" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="143">
         <v>4</v>
       </c>
       <c r="E18" s="2">
@@ -6680,13 +6856,13 @@
         <v>8</v>
       </c>
       <c r="G18" s="3">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H18" s="36">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="I18" s="68">
-        <v>190000</v>
+        <v>180000</v>
       </c>
       <c r="J18" s="71">
         <v>0</v>
@@ -6697,14 +6873,14 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="233"/>
-      <c r="B19" s="105" t="s">
-        <v>168</v>
+      <c r="A19" s="296"/>
+      <c r="B19" s="63" t="s">
+        <v>167</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>196</v>
-      </c>
-      <c r="D19" s="25">
+        <v>183</v>
+      </c>
+      <c r="D19" s="143">
         <v>4</v>
       </c>
       <c r="E19" s="2">
@@ -6714,13 +6890,13 @@
         <v>8</v>
       </c>
       <c r="G19" s="3">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H19" s="36">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="I19" s="68">
-        <v>80000</v>
+        <v>190000</v>
       </c>
       <c r="J19" s="71">
         <v>0</v>
@@ -6731,14 +6907,14 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="233"/>
-      <c r="B20" s="105" t="s">
-        <v>169</v>
+      <c r="A20" s="296"/>
+      <c r="B20" s="63" t="s">
+        <v>168</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="D20" s="25">
+        <v>196</v>
+      </c>
+      <c r="D20" s="143">
         <v>4</v>
       </c>
       <c r="E20" s="2">
@@ -6748,13 +6924,13 @@
         <v>8</v>
       </c>
       <c r="G20" s="3">
-        <v>292</v>
+        <v>60</v>
       </c>
       <c r="H20" s="36">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="I20" s="68">
-        <v>35000</v>
+        <v>80000</v>
       </c>
       <c r="J20" s="71">
         <v>0</v>
@@ -6765,14 +6941,14 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="233"/>
-      <c r="B21" s="105" t="s">
-        <v>170</v>
+      <c r="A21" s="296"/>
+      <c r="B21" s="63" t="s">
+        <v>169</v>
       </c>
       <c r="C21" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="143">
         <v>4</v>
       </c>
       <c r="E21" s="2">
@@ -6782,13 +6958,13 @@
         <v>8</v>
       </c>
       <c r="G21" s="3">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H21" s="36">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="I21" s="68">
-        <v>36000</v>
+        <v>35000</v>
       </c>
       <c r="J21" s="71">
         <v>0</v>
@@ -6799,14 +6975,14 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="233"/>
-      <c r="B22" s="105" t="s">
-        <v>207</v>
+      <c r="A22" s="296"/>
+      <c r="B22" s="63" t="s">
+        <v>170</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="D22" s="25">
+        <v>181</v>
+      </c>
+      <c r="D22" s="143">
         <v>4</v>
       </c>
       <c r="E22" s="2">
@@ -6816,13 +6992,13 @@
         <v>8</v>
       </c>
       <c r="G22" s="3">
-        <v>59</v>
+        <v>293</v>
       </c>
       <c r="H22" s="36">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="I22" s="68">
-        <v>150000</v>
+        <v>36000</v>
       </c>
       <c r="J22" s="71">
         <v>0</v>
@@ -6833,48 +7009,48 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="233"/>
-      <c r="B23" s="105" t="s">
-        <v>246</v>
+      <c r="A23" s="296"/>
+      <c r="B23" s="63" t="s">
+        <v>206</v>
       </c>
       <c r="C23" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="D23" s="25">
+      <c r="D23" s="143">
         <v>4</v>
       </c>
       <c r="E23" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F23" s="2">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="G23" s="3">
-        <v>459</v>
+        <v>59</v>
       </c>
       <c r="H23" s="36">
-        <v>1500</v>
+        <v>1270</v>
       </c>
       <c r="I23" s="68">
-        <v>100000</v>
+        <v>150000</v>
       </c>
       <c r="J23" s="71">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K23" s="53">
         <f t="shared" si="0"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="233"/>
-      <c r="B24" s="105" t="s">
-        <v>247</v>
+      <c r="A24" s="296"/>
+      <c r="B24" s="63" t="s">
+        <v>245</v>
       </c>
       <c r="C24" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="143">
         <v>4</v>
       </c>
       <c r="E24" s="2">
@@ -6884,47 +7060,47 @@
         <v>36</v>
       </c>
       <c r="G24" s="3">
-        <v>47</v>
+        <v>459</v>
       </c>
       <c r="H24" s="36">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="I24" s="68">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="J24" s="71">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K24" s="53">
         <f t="shared" si="0"/>
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="233"/>
-      <c r="B25" s="105" t="s">
-        <v>208</v>
+      <c r="A25" s="296"/>
+      <c r="B25" s="63" t="s">
+        <v>246</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="D25" s="25">
+        <v>183</v>
+      </c>
+      <c r="D25" s="143">
         <v>4</v>
       </c>
       <c r="E25" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F25" s="2">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="G25" s="3">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="H25" s="36">
-        <v>1271</v>
+        <v>1501</v>
       </c>
       <c r="I25" s="68">
-        <v>125000</v>
+        <v>200000</v>
       </c>
       <c r="J25" s="71">
         <v>0</v>
@@ -6935,30 +7111,30 @@
       </c>
     </row>
     <row r="26" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="233"/>
-      <c r="B26" s="105" t="s">
-        <v>171</v>
+      <c r="A26" s="296"/>
+      <c r="B26" s="63" t="s">
+        <v>207</v>
       </c>
       <c r="C26" s="36" t="s">
-        <v>182</v>
-      </c>
-      <c r="D26" s="25">
+        <v>181</v>
+      </c>
+      <c r="D26" s="143">
         <v>4</v>
       </c>
       <c r="E26" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F26" s="2">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="G26" s="3">
-        <v>147</v>
+        <v>39</v>
       </c>
       <c r="H26" s="36">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="I26" s="68">
-        <v>5000</v>
+        <v>125000</v>
       </c>
       <c r="J26" s="71">
         <v>0</v>
@@ -6969,14 +7145,14 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="233"/>
-      <c r="B27" s="105" t="s">
-        <v>172</v>
+      <c r="A27" s="296"/>
+      <c r="B27" s="63" t="s">
+        <v>171</v>
       </c>
       <c r="C27" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="D27" s="25">
+      <c r="D27" s="143">
         <v>4</v>
       </c>
       <c r="E27" s="2">
@@ -6986,13 +7162,13 @@
         <v>33</v>
       </c>
       <c r="G27" s="3">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H27" s="36">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="I27" s="68">
-        <v>5200</v>
+        <v>5000</v>
       </c>
       <c r="J27" s="71">
         <v>0</v>
@@ -7002,114 +7178,114 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="233"/>
-      <c r="B28" s="108" t="s">
+    <row r="28" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="296"/>
+      <c r="B28" s="63" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="D28" s="143">
+        <v>4</v>
+      </c>
+      <c r="E28" s="2">
+        <v>7</v>
+      </c>
+      <c r="F28" s="2">
+        <v>33</v>
+      </c>
+      <c r="G28" s="3">
+        <v>145</v>
+      </c>
+      <c r="H28" s="36">
+        <v>1273</v>
+      </c>
+      <c r="I28" s="68">
+        <v>5200</v>
+      </c>
+      <c r="J28" s="71">
+        <v>0</v>
+      </c>
+      <c r="K28" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="296"/>
+      <c r="B29" s="65" t="s">
         <v>173</v>
       </c>
-      <c r="C28" s="38" t="s">
+      <c r="C29" s="38" t="s">
         <v>182</v>
       </c>
-      <c r="D28" s="27">
-        <v>4</v>
-      </c>
-      <c r="E28" s="19">
+      <c r="D29" s="145">
+        <v>4</v>
+      </c>
+      <c r="E29" s="19">
         <v>7</v>
       </c>
-      <c r="F28" s="19">
+      <c r="F29" s="19">
         <v>33</v>
       </c>
-      <c r="G28" s="22">
+      <c r="G29" s="22">
         <v>144</v>
       </c>
-      <c r="H28" s="38">
+      <c r="H29" s="38">
         <v>1274</v>
       </c>
-      <c r="I28" s="73">
+      <c r="I29" s="73">
         <v>4800</v>
       </c>
-      <c r="J28" s="72">
-        <v>0</v>
-      </c>
-      <c r="K28" s="55">
+      <c r="J29" s="72">
+        <v>0</v>
+      </c>
+      <c r="K29" s="55">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="224" t="s">
+    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="222" t="s">
         <v>86</v>
       </c>
-      <c r="B29" s="152" t="s">
+      <c r="B30" s="151" t="s">
         <v>184</v>
       </c>
-      <c r="C29" s="35" t="s">
+      <c r="C30" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="D29" s="23">
-        <v>4</v>
-      </c>
-      <c r="E29" s="18">
+      <c r="D30" s="23">
+        <v>4</v>
+      </c>
+      <c r="E30" s="18">
         <v>5</v>
       </c>
-      <c r="F29" s="18">
+      <c r="F30" s="18">
         <v>9</v>
       </c>
-      <c r="G29" s="21">
+      <c r="G30" s="21">
         <v>6</v>
       </c>
-      <c r="H29" s="35">
+      <c r="H30" s="35">
         <v>1275</v>
       </c>
-      <c r="I29" s="67">
+      <c r="I30" s="67">
         <v>3000</v>
       </c>
-      <c r="J29" s="70">
-        <v>0</v>
-      </c>
-      <c r="K29" s="52">
+      <c r="J30" s="70">
+        <v>0</v>
+      </c>
+      <c r="K30" s="52">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="224"/>
-      <c r="B30" s="149" t="s">
+    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="222"/>
+      <c r="B31" s="148" t="s">
         <v>185</v>
-      </c>
-      <c r="C30" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="D30" s="25">
-        <v>4</v>
-      </c>
-      <c r="E30" s="2">
-        <v>5</v>
-      </c>
-      <c r="F30" s="2">
-        <v>9</v>
-      </c>
-      <c r="G30" s="3">
-        <v>7</v>
-      </c>
-      <c r="H30" s="36">
-        <v>1276</v>
-      </c>
-      <c r="I30" s="68">
-        <v>6000</v>
-      </c>
-      <c r="J30" s="71">
-        <v>0</v>
-      </c>
-      <c r="K30" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="224"/>
-      <c r="B31" s="149" t="s">
-        <v>186</v>
       </c>
       <c r="C31" s="36" t="s">
         <v>152</v>
@@ -7121,16 +7297,16 @@
         <v>5</v>
       </c>
       <c r="F31" s="2">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="G31" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H31" s="36">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="I31" s="68">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="J31" s="71">
         <v>0</v>
@@ -7141,30 +7317,30 @@
       </c>
     </row>
     <row r="32" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="224"/>
-      <c r="B32" s="149" t="s">
-        <v>187</v>
+      <c r="A32" s="222"/>
+      <c r="B32" s="148" t="s">
+        <v>186</v>
       </c>
       <c r="C32" s="36" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="D32" s="25">
         <v>4</v>
       </c>
       <c r="E32" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F32" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G32" s="3">
-        <v>442</v>
+        <v>4</v>
       </c>
       <c r="H32" s="36">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="I32" s="68">
-        <v>2500</v>
+        <v>8000</v>
       </c>
       <c r="J32" s="71">
         <v>0</v>
@@ -7175,9 +7351,9 @@
       </c>
     </row>
     <row r="33" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="224"/>
-      <c r="B33" s="149" t="s">
-        <v>188</v>
+      <c r="A33" s="222"/>
+      <c r="B33" s="148" t="s">
+        <v>187</v>
       </c>
       <c r="C33" s="36" t="s">
         <v>182</v>
@@ -7192,13 +7368,13 @@
         <v>33</v>
       </c>
       <c r="G33" s="3">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H33" s="36">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="I33" s="68">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="J33" s="71">
         <v>0</v>
@@ -7209,9 +7385,9 @@
       </c>
     </row>
     <row r="34" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="224"/>
-      <c r="B34" s="149" t="s">
-        <v>189</v>
+      <c r="A34" s="222"/>
+      <c r="B34" s="148" t="s">
+        <v>188</v>
       </c>
       <c r="C34" s="36" t="s">
         <v>182</v>
@@ -7226,13 +7402,13 @@
         <v>33</v>
       </c>
       <c r="G34" s="3">
-        <v>32</v>
+        <v>441</v>
       </c>
       <c r="H34" s="36">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="I34" s="68">
-        <v>6000</v>
+        <v>2400</v>
       </c>
       <c r="J34" s="71">
         <v>0</v>
@@ -7243,9 +7419,9 @@
       </c>
     </row>
     <row r="35" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="224"/>
-      <c r="B35" s="149" t="s">
-        <v>190</v>
+      <c r="A35" s="222"/>
+      <c r="B35" s="148" t="s">
+        <v>189</v>
       </c>
       <c r="C35" s="36" t="s">
         <v>182</v>
@@ -7260,13 +7436,13 @@
         <v>33</v>
       </c>
       <c r="G35" s="3">
-        <v>155</v>
+        <v>32</v>
       </c>
       <c r="H35" s="36">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="I35" s="68">
-        <v>8500</v>
+        <v>6000</v>
       </c>
       <c r="J35" s="71">
         <v>0</v>
@@ -7277,30 +7453,30 @@
       </c>
     </row>
     <row r="36" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="224"/>
-      <c r="B36" s="149" t="s">
-        <v>228</v>
+      <c r="A36" s="222"/>
+      <c r="B36" s="148" t="s">
+        <v>190</v>
       </c>
       <c r="C36" s="36" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D36" s="25">
         <v>4</v>
       </c>
       <c r="E36" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F36" s="2">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="G36" s="3">
-        <v>353</v>
+        <v>155</v>
       </c>
       <c r="H36" s="36">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="I36" s="68">
-        <v>100000</v>
+        <v>8500</v>
       </c>
       <c r="J36" s="71">
         <v>0</v>
@@ -7311,9 +7487,9 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="224"/>
-      <c r="B37" s="149" t="s">
-        <v>229</v>
+      <c r="A37" s="222"/>
+      <c r="B37" s="148" t="s">
+        <v>227</v>
       </c>
       <c r="C37" s="36" t="s">
         <v>181</v>
@@ -7328,13 +7504,13 @@
         <v>8</v>
       </c>
       <c r="G37" s="3">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H37" s="36">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="I37" s="68">
-        <v>80000</v>
+        <v>100000</v>
       </c>
       <c r="J37" s="71">
         <v>0</v>
@@ -7345,9 +7521,9 @@
       </c>
     </row>
     <row r="38" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="224"/>
-      <c r="B38" s="149" t="s">
-        <v>226</v>
+      <c r="A38" s="222"/>
+      <c r="B38" s="148" t="s">
+        <v>228</v>
       </c>
       <c r="C38" s="36" t="s">
         <v>181</v>
@@ -7362,13 +7538,13 @@
         <v>8</v>
       </c>
       <c r="G38" s="3">
-        <v>58</v>
+        <v>354</v>
       </c>
       <c r="H38" s="36">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="I38" s="68">
-        <v>135000</v>
+        <v>80000</v>
       </c>
       <c r="J38" s="71">
         <v>0</v>
@@ -7379,12 +7555,12 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="224"/>
-      <c r="B39" s="149" t="s">
-        <v>193</v>
+      <c r="A39" s="222"/>
+      <c r="B39" s="148" t="s">
+        <v>225</v>
       </c>
       <c r="C39" s="36" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="D39" s="25">
         <v>4</v>
@@ -7396,13 +7572,13 @@
         <v>8</v>
       </c>
       <c r="G39" s="3">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="H39" s="36">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="I39" s="68">
-        <v>1000000</v>
+        <v>135000</v>
       </c>
       <c r="J39" s="71">
         <v>0</v>
@@ -7413,12 +7589,12 @@
       </c>
     </row>
     <row r="40" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="224"/>
-      <c r="B40" s="149" t="s">
-        <v>227</v>
+      <c r="A40" s="222"/>
+      <c r="B40" s="148" t="s">
+        <v>193</v>
       </c>
       <c r="C40" s="36" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="D40" s="25">
         <v>4</v>
@@ -7430,13 +7606,13 @@
         <v>8</v>
       </c>
       <c r="G40" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H40" s="36">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="I40" s="68">
-        <v>450000</v>
+        <v>1000000</v>
       </c>
       <c r="J40" s="71">
         <v>0</v>
@@ -7445,15 +7621,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L40" s="122"/>
     </row>
     <row r="41" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="224"/>
-      <c r="B41" s="149" t="s">
-        <v>194</v>
+      <c r="A41" s="222"/>
+      <c r="B41" s="148" t="s">
+        <v>226</v>
       </c>
       <c r="C41" s="36" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="D41" s="25">
         <v>4</v>
@@ -7465,13 +7640,13 @@
         <v>8</v>
       </c>
       <c r="G41" s="3">
-        <v>287</v>
+        <v>45</v>
       </c>
       <c r="H41" s="36">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="I41" s="68">
-        <v>600000</v>
+        <v>450000</v>
       </c>
       <c r="J41" s="71">
         <v>0</v>
@@ -7480,115 +7655,116 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="225"/>
-      <c r="B42" s="154" t="s">
+      <c r="L41" s="121"/>
+    </row>
+    <row r="42" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="222"/>
+      <c r="B42" s="148" t="s">
+        <v>194</v>
+      </c>
+      <c r="C42" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="D42" s="25">
+        <v>4</v>
+      </c>
+      <c r="E42" s="2">
+        <v>4</v>
+      </c>
+      <c r="F42" s="2">
+        <v>8</v>
+      </c>
+      <c r="G42" s="3">
+        <v>287</v>
+      </c>
+      <c r="H42" s="36">
+        <v>1287</v>
+      </c>
+      <c r="I42" s="68">
+        <v>600000</v>
+      </c>
+      <c r="J42" s="71">
+        <v>0</v>
+      </c>
+      <c r="K42" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="223"/>
+      <c r="B43" s="153" t="s">
         <v>195</v>
       </c>
-      <c r="C42" s="38" t="s">
+      <c r="C43" s="38" t="s">
         <v>183</v>
       </c>
-      <c r="D42" s="27">
-        <v>4</v>
-      </c>
-      <c r="E42" s="19">
-        <v>4</v>
-      </c>
-      <c r="F42" s="19">
+      <c r="D43" s="27">
+        <v>4</v>
+      </c>
+      <c r="E43" s="19">
+        <v>4</v>
+      </c>
+      <c r="F43" s="19">
         <v>8</v>
       </c>
-      <c r="G42" s="22">
+      <c r="G43" s="22">
         <v>75</v>
       </c>
-      <c r="H42" s="38">
+      <c r="H43" s="38">
         <v>1288</v>
       </c>
-      <c r="I42" s="73">
+      <c r="I43" s="73">
         <v>550000</v>
       </c>
-      <c r="J42" s="72">
-        <v>0</v>
-      </c>
-      <c r="K42" s="55">
+      <c r="J43" s="72">
+        <v>0</v>
+      </c>
+      <c r="K43" s="55">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="226" t="s">
+    <row r="44" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="224" t="s">
         <v>87</v>
       </c>
-      <c r="B43" s="155" t="s">
+      <c r="B44" s="154" t="s">
+        <v>198</v>
+      </c>
+      <c r="C44" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="D44" s="23">
+        <v>4</v>
+      </c>
+      <c r="E44" s="18">
+        <v>4</v>
+      </c>
+      <c r="F44" s="18">
+        <v>8</v>
+      </c>
+      <c r="G44" s="21">
+        <v>305</v>
+      </c>
+      <c r="H44" s="35">
+        <v>1289</v>
+      </c>
+      <c r="I44" s="67">
+        <v>600000</v>
+      </c>
+      <c r="J44" s="70">
+        <v>0</v>
+      </c>
+      <c r="K44" s="52">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="225"/>
+      <c r="B45" s="149" t="s">
         <v>199</v>
-      </c>
-      <c r="C43" s="35" t="s">
-        <v>196</v>
-      </c>
-      <c r="D43" s="23">
-        <v>4</v>
-      </c>
-      <c r="E43" s="18">
-        <v>4</v>
-      </c>
-      <c r="F43" s="18">
-        <v>8</v>
-      </c>
-      <c r="G43" s="21">
-        <v>305</v>
-      </c>
-      <c r="H43" s="35">
-        <v>1289</v>
-      </c>
-      <c r="I43" s="67">
-        <v>600000</v>
-      </c>
-      <c r="J43" s="70">
-        <v>0</v>
-      </c>
-      <c r="K43" s="52">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="227"/>
-      <c r="B44" s="150" t="s">
-        <v>200</v>
-      </c>
-      <c r="C44" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="D44" s="25">
-        <v>4</v>
-      </c>
-      <c r="E44" s="2">
-        <v>4</v>
-      </c>
-      <c r="F44" s="2">
-        <v>8</v>
-      </c>
-      <c r="G44" s="3">
-        <v>295</v>
-      </c>
-      <c r="H44" s="36">
-        <v>1290</v>
-      </c>
-      <c r="I44" s="68">
-        <v>450000</v>
-      </c>
-      <c r="J44" s="71">
-        <v>0</v>
-      </c>
-      <c r="K44" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="227"/>
-      <c r="B45" s="150" t="s">
-        <v>201</v>
       </c>
       <c r="C45" s="36" t="s">
         <v>183</v>
@@ -7603,13 +7779,13 @@
         <v>8</v>
       </c>
       <c r="G45" s="3">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H45" s="36">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="I45" s="68">
-        <v>440000</v>
+        <v>450000</v>
       </c>
       <c r="J45" s="71">
         <v>0</v>
@@ -7620,9 +7796,9 @@
       </c>
     </row>
     <row r="46" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="227"/>
-      <c r="B46" s="150" t="s">
-        <v>174</v>
+      <c r="A46" s="225"/>
+      <c r="B46" s="149" t="s">
+        <v>200</v>
       </c>
       <c r="C46" s="36" t="s">
         <v>183</v>
@@ -7637,13 +7813,13 @@
         <v>8</v>
       </c>
       <c r="G46" s="3">
-        <v>432</v>
+        <v>298</v>
       </c>
       <c r="H46" s="36">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="I46" s="68">
-        <v>80000</v>
+        <v>440000</v>
       </c>
       <c r="J46" s="71">
         <v>0</v>
@@ -7654,9 +7830,9 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="227"/>
-      <c r="B47" s="150" t="s">
-        <v>175</v>
+      <c r="A47" s="225"/>
+      <c r="B47" s="149" t="s">
+        <v>174</v>
       </c>
       <c r="C47" s="36" t="s">
         <v>183</v>
@@ -7671,13 +7847,13 @@
         <v>8</v>
       </c>
       <c r="G47" s="3">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H47" s="36">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="I47" s="68">
-        <v>50000</v>
+        <v>80000</v>
       </c>
       <c r="J47" s="71">
         <v>0</v>
@@ -7688,12 +7864,12 @@
       </c>
     </row>
     <row r="48" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="227"/>
-      <c r="B48" s="150" t="s">
-        <v>176</v>
+      <c r="A48" s="225"/>
+      <c r="B48" s="149" t="s">
+        <v>175</v>
       </c>
       <c r="C48" s="36" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="D48" s="25">
         <v>4</v>
@@ -7705,13 +7881,13 @@
         <v>8</v>
       </c>
       <c r="G48" s="3">
-        <v>362</v>
+        <v>433</v>
       </c>
       <c r="H48" s="36">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="I48" s="68">
-        <v>950000</v>
+        <v>50000</v>
       </c>
       <c r="J48" s="71">
         <v>0</v>
@@ -7722,12 +7898,12 @@
       </c>
     </row>
     <row r="49" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="227"/>
-      <c r="B49" s="150" t="s">
-        <v>177</v>
+      <c r="A49" s="225"/>
+      <c r="B49" s="149" t="s">
+        <v>176</v>
       </c>
       <c r="C49" s="36" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="D49" s="25">
         <v>4</v>
@@ -7739,13 +7915,13 @@
         <v>8</v>
       </c>
       <c r="G49" s="3">
-        <v>304</v>
+        <v>362</v>
       </c>
       <c r="H49" s="36">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="I49" s="68">
-        <v>1300000</v>
+        <v>950000</v>
       </c>
       <c r="J49" s="71">
         <v>0</v>
@@ -7755,127 +7931,127 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="228"/>
-      <c r="B50" s="163" t="s">
+    <row r="50" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="225"/>
+      <c r="B50" s="149" t="s">
+        <v>177</v>
+      </c>
+      <c r="C50" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="D50" s="25">
+        <v>4</v>
+      </c>
+      <c r="E50" s="2">
+        <v>4</v>
+      </c>
+      <c r="F50" s="2">
+        <v>8</v>
+      </c>
+      <c r="G50" s="3">
+        <v>304</v>
+      </c>
+      <c r="H50" s="36">
+        <v>1295</v>
+      </c>
+      <c r="I50" s="68">
+        <v>1300000</v>
+      </c>
+      <c r="J50" s="71">
+        <v>0</v>
+      </c>
+      <c r="K50" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="226"/>
+      <c r="B51" s="162" t="s">
         <v>180</v>
       </c>
-      <c r="C50" s="38" t="s">
+      <c r="C51" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="D50" s="27">
-        <v>4</v>
-      </c>
-      <c r="E50" s="19">
-        <v>4</v>
-      </c>
-      <c r="F50" s="19">
+      <c r="D51" s="27">
+        <v>4</v>
+      </c>
+      <c r="E51" s="19">
+        <v>4</v>
+      </c>
+      <c r="F51" s="19">
         <v>8</v>
       </c>
-      <c r="G50" s="22">
+      <c r="G51" s="22">
         <v>298</v>
       </c>
-      <c r="H50" s="38">
+      <c r="H51" s="38">
         <v>1296</v>
       </c>
-      <c r="I50" s="69">
+      <c r="I51" s="69">
         <v>35000</v>
       </c>
-      <c r="J50" s="142">
-        <v>0</v>
-      </c>
-      <c r="K50" s="158">
+      <c r="J51" s="141">
+        <v>0</v>
+      </c>
+      <c r="K51" s="157">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="229" t="s">
+    <row r="52" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="227" t="s">
         <v>88</v>
       </c>
-      <c r="B51" s="113" t="s">
+      <c r="B52" s="113" t="s">
         <v>178</v>
       </c>
-      <c r="C51" s="35" t="s">
+      <c r="C52" s="35" t="s">
         <v>182</v>
       </c>
-      <c r="D51" s="23"/>
-      <c r="E51" s="18"/>
-      <c r="F51" s="18"/>
-      <c r="G51" s="21"/>
-      <c r="H51" s="35">
+      <c r="D52" s="23"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="21"/>
+      <c r="H52" s="35">
         <v>1297</v>
       </c>
-      <c r="I51" s="67">
-        <v>0</v>
-      </c>
-      <c r="J51" s="70">
-        <v>0</v>
-      </c>
-      <c r="K51" s="52">
+      <c r="I52" s="67">
+        <v>0</v>
+      </c>
+      <c r="J52" s="70">
+        <v>0</v>
+      </c>
+      <c r="K52" s="52">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="230"/>
-      <c r="B52" s="151" t="s">
-        <v>205</v>
-      </c>
-      <c r="C52" s="36" t="s">
+    <row r="53" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="228"/>
+      <c r="B53" s="150" t="s">
+        <v>204</v>
+      </c>
+      <c r="C53" s="36" t="s">
         <v>152</v>
       </c>
-      <c r="D52" s="25">
-        <v>4</v>
-      </c>
-      <c r="E52" s="2">
+      <c r="D53" s="25">
+        <v>4</v>
+      </c>
+      <c r="E53" s="2">
         <v>5</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F53" s="2">
         <v>9</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G53" s="3">
         <v>389</v>
       </c>
-      <c r="H52" s="36">
+      <c r="H53" s="36">
         <v>1298</v>
       </c>
-      <c r="I52" s="68">
+      <c r="I53" s="68">
         <v>2000</v>
-      </c>
-      <c r="J52" s="71">
-        <v>0</v>
-      </c>
-      <c r="K52" s="53">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="230"/>
-      <c r="B53" s="151" t="s">
-        <v>179</v>
-      </c>
-      <c r="C53" s="36" t="s">
-        <v>182</v>
-      </c>
-      <c r="D53" s="25">
-        <v>4</v>
-      </c>
-      <c r="E53" s="2">
-        <v>7</v>
-      </c>
-      <c r="F53" s="2">
-        <v>33</v>
-      </c>
-      <c r="G53" s="3">
-        <v>376</v>
-      </c>
-      <c r="H53" s="36">
-        <v>1299</v>
-      </c>
-      <c r="I53" s="68">
-        <v>2500</v>
       </c>
       <c r="J53" s="71">
         <v>0</v>
@@ -7884,66 +8060,280 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L53" s="122"/>
-    </row>
-    <row r="54" spans="1:12" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="231"/>
-      <c r="B54" s="106" t="s">
-        <v>230</v>
+    </row>
+    <row r="54" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="228"/>
+      <c r="B54" s="150" t="s">
+        <v>251</v>
       </c>
       <c r="C54" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="D54" s="25">
+        <v>4</v>
+      </c>
+      <c r="E54" s="2">
+        <v>7</v>
+      </c>
+      <c r="F54" s="2">
+        <v>33</v>
+      </c>
+      <c r="G54" s="3">
+        <v>380</v>
+      </c>
+      <c r="H54" s="36">
+        <v>1303</v>
+      </c>
+      <c r="I54" s="68">
+        <v>2800</v>
+      </c>
+      <c r="J54" s="71">
+        <v>0</v>
+      </c>
+      <c r="K54" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="228"/>
+      <c r="B55" s="150" t="s">
+        <v>179</v>
+      </c>
+      <c r="C55" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="D55" s="25">
+        <v>4</v>
+      </c>
+      <c r="E55" s="2">
+        <v>7</v>
+      </c>
+      <c r="F55" s="2">
+        <v>33</v>
+      </c>
+      <c r="G55" s="3">
+        <v>376</v>
+      </c>
+      <c r="H55" s="36">
+        <v>1299</v>
+      </c>
+      <c r="I55" s="68">
+        <v>2500</v>
+      </c>
+      <c r="J55" s="71">
+        <v>0</v>
+      </c>
+      <c r="K55" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L55" s="121"/>
+    </row>
+    <row r="56" spans="1:12" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="229"/>
+      <c r="B56" s="283" t="s">
+        <v>229</v>
+      </c>
+      <c r="C56" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="D54" s="27">
-        <v>4</v>
-      </c>
-      <c r="E54" s="19">
-        <v>4</v>
-      </c>
-      <c r="F54" s="19">
+      <c r="D56" s="34">
+        <v>4</v>
+      </c>
+      <c r="E56" s="17">
+        <v>4</v>
+      </c>
+      <c r="F56" s="17">
         <v>8</v>
       </c>
-      <c r="G54" s="22">
+      <c r="G56" s="33">
         <v>407</v>
       </c>
-      <c r="H54" s="38">
+      <c r="H56" s="37">
         <v>1300</v>
       </c>
-      <c r="I54" s="73">
+      <c r="I56" s="69">
         <v>80000</v>
       </c>
-      <c r="J54" s="72">
-        <v>0</v>
-      </c>
-      <c r="K54" s="55">
+      <c r="J56" s="141">
+        <v>0</v>
+      </c>
+      <c r="K56" s="157">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="I55" s="215" t="s">
+    <row r="57" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="312" t="s">
+        <v>248</v>
+      </c>
+      <c r="B57" s="284" t="s">
+        <v>253</v>
+      </c>
+      <c r="C57" s="87" t="s">
+        <v>152</v>
+      </c>
+      <c r="D57" s="125">
+        <v>4</v>
+      </c>
+      <c r="E57" s="18">
+        <v>5</v>
+      </c>
+      <c r="F57" s="18">
+        <v>9</v>
+      </c>
+      <c r="G57" s="24">
+        <v>11033</v>
+      </c>
+      <c r="H57" s="35">
+        <v>1501</v>
+      </c>
+      <c r="I57" s="52">
+        <v>5400</v>
+      </c>
+      <c r="J57" s="70">
+        <v>0</v>
+      </c>
+      <c r="K57" s="52">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="313"/>
+      <c r="B58" s="311" t="s">
+        <v>254</v>
+      </c>
+      <c r="C58" s="66" t="s">
+        <v>152</v>
+      </c>
+      <c r="D58" s="143">
+        <v>4</v>
+      </c>
+      <c r="E58" s="2">
+        <v>5</v>
+      </c>
+      <c r="F58" s="2">
+        <v>9</v>
+      </c>
+      <c r="G58" s="26">
+        <v>11034</v>
+      </c>
+      <c r="H58" s="36">
+        <v>1502</v>
+      </c>
+      <c r="I58" s="53">
+        <v>5000</v>
+      </c>
+      <c r="J58" s="71">
+        <v>0</v>
+      </c>
+      <c r="K58" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="313"/>
+      <c r="B59" s="311" t="s">
+        <v>255</v>
+      </c>
+      <c r="C59" s="66" t="s">
+        <v>183</v>
+      </c>
+      <c r="D59" s="143">
+        <v>4</v>
+      </c>
+      <c r="E59" s="2">
+        <v>4</v>
+      </c>
+      <c r="F59" s="2">
+        <v>8</v>
+      </c>
+      <c r="G59" s="26">
+        <v>11031</v>
+      </c>
+      <c r="H59" s="36">
+        <v>1500</v>
+      </c>
+      <c r="I59" s="53">
+        <v>450000</v>
+      </c>
+      <c r="J59" s="71">
+        <v>0</v>
+      </c>
+      <c r="K59" s="53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="314"/>
+      <c r="B60" s="285" t="s">
+        <v>256</v>
+      </c>
+      <c r="C60" s="88" t="s">
+        <v>252</v>
+      </c>
+      <c r="D60" s="145">
+        <v>4</v>
+      </c>
+      <c r="E60" s="19">
+        <v>4</v>
+      </c>
+      <c r="F60" s="19">
+        <v>8</v>
+      </c>
+      <c r="G60" s="28">
+        <v>11093</v>
+      </c>
+      <c r="H60" s="38">
+        <v>1503</v>
+      </c>
+      <c r="I60" s="55">
+        <v>1100000</v>
+      </c>
+      <c r="J60" s="72">
+        <v>2</v>
+      </c>
+      <c r="K60" s="55">
+        <f t="shared" si="0"/>
+        <v>2200000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B61" s="317"/>
+      <c r="I61" s="230" t="s">
         <v>43</v>
       </c>
-      <c r="J55" s="216"/>
-      <c r="K55" s="219">
-        <f>SUM(K2:K54)</f>
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I56" s="217"/>
-      <c r="J56" s="218"/>
-      <c r="K56" s="220"/>
+      <c r="J61" s="310"/>
+      <c r="K61" s="217">
+        <f>SUM(K2:K60)</f>
+        <v>2200000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I62" s="215"/>
+      <c r="J62" s="216"/>
+      <c r="K62" s="218"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H63" s="194"/>
+    </row>
+    <row r="65" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H65" s="194"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="I55:J56"/>
-    <mergeCell ref="K55:K56"/>
+  <mergeCells count="8">
+    <mergeCell ref="I61:J62"/>
+    <mergeCell ref="K61:K62"/>
     <mergeCell ref="D1:G1"/>
-    <mergeCell ref="A29:A42"/>
-    <mergeCell ref="A43:A50"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="A2:A28"/>
+    <mergeCell ref="A30:A43"/>
+    <mergeCell ref="A44:A51"/>
+    <mergeCell ref="A52:A56"/>
+    <mergeCell ref="A2:A29"/>
+    <mergeCell ref="A57:A60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -7967,16 +8357,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="125"/>
+      <c r="A1" s="124"/>
       <c r="B1" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="C1" s="221" t="s">
+      <c r="C1" s="219" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="222"/>
-      <c r="E1" s="222"/>
-      <c r="F1" s="223"/>
+      <c r="D1" s="220"/>
+      <c r="E1" s="220"/>
+      <c r="F1" s="221"/>
       <c r="G1" s="15" t="s">
         <v>39</v>
       </c>
@@ -7991,13 +8381,13 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="237" t="s">
+      <c r="A2" s="233" t="s">
         <v>123</v>
       </c>
       <c r="B2" s="59" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="126">
+      <c r="C2" s="125">
         <v>1</v>
       </c>
       <c r="D2" s="18">
@@ -8022,11 +8412,11 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="238"/>
+      <c r="A3" s="234"/>
       <c r="B3" s="60" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="127">
+      <c r="C3" s="126">
         <v>1</v>
       </c>
       <c r="D3" s="4">
@@ -8051,11 +8441,11 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="238"/>
+      <c r="A4" s="234"/>
       <c r="B4" s="60" t="s">
         <v>107</v>
       </c>
-      <c r="C4" s="127">
+      <c r="C4" s="126">
         <v>1</v>
       </c>
       <c r="D4" s="4">
@@ -8080,11 +8470,11 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="238"/>
-      <c r="B5" s="128" t="s">
+      <c r="A5" s="234"/>
+      <c r="B5" s="127" t="s">
         <v>108</v>
       </c>
-      <c r="C5" s="127">
+      <c r="C5" s="126">
         <v>1</v>
       </c>
       <c r="D5" s="4">
@@ -8109,11 +8499,11 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="238"/>
+      <c r="A6" s="234"/>
       <c r="B6" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="C6" s="127">
+      <c r="C6" s="126">
         <v>1</v>
       </c>
       <c r="D6" s="4">
@@ -8138,11 +8528,11 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="238"/>
+      <c r="A7" s="234"/>
       <c r="B7" s="60" t="s">
         <v>109</v>
       </c>
-      <c r="C7" s="127">
+      <c r="C7" s="126">
         <v>1</v>
       </c>
       <c r="D7" s="4">
@@ -8167,11 +8557,11 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="238"/>
+      <c r="A8" s="234"/>
       <c r="B8" s="60" t="s">
         <v>110</v>
       </c>
-      <c r="C8" s="127">
+      <c r="C8" s="126">
         <v>1</v>
       </c>
       <c r="D8" s="4">
@@ -8196,11 +8586,11 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="238"/>
+      <c r="A9" s="234"/>
       <c r="B9" s="60" t="s">
         <v>115</v>
       </c>
-      <c r="C9" s="127">
+      <c r="C9" s="126">
         <v>1</v>
       </c>
       <c r="D9" s="4">
@@ -8225,11 +8615,11 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="238"/>
+      <c r="A10" s="234"/>
       <c r="B10" s="60" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="127">
+      <c r="C10" s="126">
         <v>1</v>
       </c>
       <c r="D10" s="4">
@@ -8254,11 +8644,11 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="238"/>
+      <c r="A11" s="234"/>
       <c r="B11" s="60" t="s">
         <v>111</v>
       </c>
-      <c r="C11" s="127">
+      <c r="C11" s="126">
         <v>1</v>
       </c>
       <c r="D11" s="4">
@@ -8283,11 +8673,11 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="238"/>
+      <c r="A12" s="234"/>
       <c r="B12" s="60" t="s">
         <v>112</v>
       </c>
-      <c r="C12" s="127">
+      <c r="C12" s="126">
         <v>1</v>
       </c>
       <c r="D12" s="4">
@@ -8312,11 +8702,11 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="238"/>
+      <c r="A13" s="234"/>
       <c r="B13" s="60" t="s">
         <v>113</v>
       </c>
-      <c r="C13" s="127">
+      <c r="C13" s="126">
         <v>1</v>
       </c>
       <c r="D13" s="4">
@@ -8341,11 +8731,11 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="238"/>
+      <c r="A14" s="234"/>
       <c r="B14" s="60" t="s">
         <v>114</v>
       </c>
-      <c r="C14" s="127">
+      <c r="C14" s="126">
         <v>1</v>
       </c>
       <c r="D14" s="4">
@@ -8370,11 +8760,11 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="238"/>
+      <c r="A15" s="234"/>
       <c r="B15" s="60" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="127">
+      <c r="C15" s="126">
         <v>1</v>
       </c>
       <c r="D15" s="4">
@@ -8399,11 +8789,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="238"/>
+      <c r="A16" s="234"/>
       <c r="B16" s="60" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="127">
+      <c r="C16" s="126">
         <v>1</v>
       </c>
       <c r="D16" s="4">
@@ -8428,11 +8818,11 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="238"/>
+      <c r="A17" s="234"/>
       <c r="B17" s="60" t="s">
         <v>119</v>
       </c>
-      <c r="C17" s="127">
+      <c r="C17" s="126">
         <v>1</v>
       </c>
       <c r="D17" s="4">
@@ -8457,11 +8847,11 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="238"/>
+      <c r="A18" s="234"/>
       <c r="B18" s="60" t="s">
         <v>120</v>
       </c>
-      <c r="C18" s="127">
+      <c r="C18" s="126">
         <v>1</v>
       </c>
       <c r="D18" s="4">
@@ -8486,23 +8876,23 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="239"/>
-      <c r="B19" s="147" t="s">
+      <c r="A19" s="235"/>
+      <c r="B19" s="146" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="139">
-        <v>1</v>
-      </c>
-      <c r="D19" s="140">
+      <c r="C19" s="138">
+        <v>1</v>
+      </c>
+      <c r="D19" s="139">
         <v>3</v>
       </c>
-      <c r="E19" s="140">
+      <c r="E19" s="139">
         <v>43</v>
       </c>
       <c r="F19" s="33">
         <v>855</v>
       </c>
-      <c r="G19" s="143">
+      <c r="G19" s="142">
         <v>1267</v>
       </c>
       <c r="H19" s="55">
@@ -8515,13 +8905,13 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="240" t="s">
+      <c r="A20" s="236" t="s">
         <v>141</v>
       </c>
       <c r="B20" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="C20" s="126">
+      <c r="C20" s="125">
         <v>4</v>
       </c>
       <c r="D20" s="18">
@@ -8546,11 +8936,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="241"/>
+      <c r="A21" s="237"/>
       <c r="B21" s="60" t="s">
         <v>139</v>
       </c>
-      <c r="C21" s="144">
+      <c r="C21" s="143">
         <v>4</v>
       </c>
       <c r="D21" s="2">
@@ -8575,11 +8965,11 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="241"/>
+      <c r="A22" s="237"/>
       <c r="B22" s="60" t="s">
         <v>132</v>
       </c>
-      <c r="C22" s="144">
+      <c r="C22" s="143">
         <v>4</v>
       </c>
       <c r="D22" s="2">
@@ -8604,11 +8994,11 @@
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="241"/>
+      <c r="A23" s="237"/>
       <c r="B23" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="C23" s="144">
+      <c r="C23" s="143">
         <v>4</v>
       </c>
       <c r="D23" s="2">
@@ -8633,11 +9023,11 @@
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="241"/>
+      <c r="A24" s="237"/>
       <c r="B24" s="60" t="s">
         <v>128</v>
       </c>
-      <c r="C24" s="144">
+      <c r="C24" s="143">
         <v>4</v>
       </c>
       <c r="D24" s="2">
@@ -8662,11 +9052,11 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="241"/>
+      <c r="A25" s="237"/>
       <c r="B25" s="60" t="s">
         <v>147</v>
       </c>
-      <c r="C25" s="145">
+      <c r="C25" s="144">
         <v>4</v>
       </c>
       <c r="D25" s="17">
@@ -8684,18 +9074,18 @@
       <c r="H25" s="69">
         <v>720000</v>
       </c>
-      <c r="I25" s="142"/>
+      <c r="I25" s="141"/>
       <c r="J25" s="69">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="241"/>
+      <c r="A26" s="237"/>
       <c r="B26" s="60" t="s">
         <v>191</v>
       </c>
-      <c r="C26" s="145">
+      <c r="C26" s="144">
         <v>4</v>
       </c>
       <c r="D26" s="17">
@@ -8713,18 +9103,18 @@
       <c r="H26" s="69">
         <v>900000</v>
       </c>
-      <c r="I26" s="142"/>
+      <c r="I26" s="141"/>
       <c r="J26" s="69">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="242"/>
+      <c r="A27" s="238"/>
       <c r="B27" s="61" t="s">
         <v>135</v>
       </c>
-      <c r="C27" s="146">
+      <c r="C27" s="145">
         <v>4</v>
       </c>
       <c r="D27" s="19">
@@ -8749,10 +9139,10 @@
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="243" t="s">
+      <c r="A28" s="239" t="s">
         <v>143</v>
       </c>
-      <c r="B28" s="131" t="s">
+      <c r="B28" s="130" t="s">
         <v>136</v>
       </c>
       <c r="C28" s="30">
@@ -8764,7 +9154,7 @@
       <c r="E28" s="4">
         <v>48</v>
       </c>
-      <c r="F28" s="141">
+      <c r="F28" s="140">
         <v>1170</v>
       </c>
       <c r="G28" s="42">
@@ -8780,8 +9170,8 @@
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="244"/>
-      <c r="B29" s="130" t="s">
+      <c r="A29" s="240"/>
+      <c r="B29" s="129" t="s">
         <v>137</v>
       </c>
       <c r="C29" s="25">
@@ -8809,8 +9199,8 @@
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="244"/>
-      <c r="B30" s="130" t="s">
+      <c r="A30" s="240"/>
+      <c r="B30" s="129" t="s">
         <v>131</v>
       </c>
       <c r="C30" s="25">
@@ -8838,8 +9228,8 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="245"/>
-      <c r="B31" s="132" t="s">
+      <c r="A31" s="241"/>
+      <c r="B31" s="131" t="s">
         <v>138</v>
       </c>
       <c r="C31" s="27">
@@ -8854,7 +9244,7 @@
       <c r="F31" s="28">
         <v>666</v>
       </c>
-      <c r="G31" s="124">
+      <c r="G31" s="123">
         <v>1277</v>
       </c>
       <c r="H31" s="55">
@@ -8867,10 +9257,10 @@
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="246" t="s">
+      <c r="A32" s="242" t="s">
         <v>144</v>
       </c>
-      <c r="B32" s="129" t="s">
+      <c r="B32" s="128" t="s">
         <v>126</v>
       </c>
       <c r="C32" s="23">
@@ -8892,16 +9282,16 @@
         <v>2300000</v>
       </c>
       <c r="I32" s="70">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J32" s="52">
         <f t="shared" si="0"/>
-        <v>9200000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="247"/>
-      <c r="B33" s="130" t="s">
+      <c r="A33" s="243"/>
+      <c r="B33" s="129" t="s">
         <v>129</v>
       </c>
       <c r="C33" s="25">
@@ -8923,16 +9313,16 @@
         <v>1440000</v>
       </c>
       <c r="I33" s="71">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J33" s="53">
         <f t="shared" si="0"/>
-        <v>2880000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="247"/>
-      <c r="B34" s="130" t="s">
+      <c r="A34" s="243"/>
+      <c r="B34" s="129" t="s">
         <v>133</v>
       </c>
       <c r="C34" s="25">
@@ -8954,16 +9344,16 @@
         <v>1100000</v>
       </c>
       <c r="I34" s="71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="53">
         <f t="shared" si="0"/>
-        <v>1100000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="247"/>
-      <c r="B35" s="130" t="s">
+      <c r="A35" s="243"/>
+      <c r="B35" s="129" t="s">
         <v>134</v>
       </c>
       <c r="C35" s="25">
@@ -8985,16 +9375,16 @@
         <v>1250000</v>
       </c>
       <c r="I35" s="71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" s="53">
         <f t="shared" si="0"/>
-        <v>1250000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="247"/>
-      <c r="B36" s="130" t="s">
+      <c r="A36" s="243"/>
+      <c r="B36" s="129" t="s">
         <v>125</v>
       </c>
       <c r="C36" s="25">
@@ -9016,16 +9406,16 @@
         <v>1600000</v>
       </c>
       <c r="I36" s="71">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" s="53">
         <f t="shared" si="0"/>
-        <v>3200000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="247"/>
-      <c r="B37" s="130" t="s">
+      <c r="A37" s="243"/>
+      <c r="B37" s="129" t="s">
         <v>192</v>
       </c>
       <c r="C37" s="25">
@@ -9047,16 +9437,16 @@
         <v>1800000</v>
       </c>
       <c r="I37" s="71">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J37" s="53">
         <f t="shared" si="0"/>
-        <v>3600000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="247"/>
-      <c r="B38" s="130" t="s">
+      <c r="A38" s="243"/>
+      <c r="B38" s="129" t="s">
         <v>130</v>
       </c>
       <c r="C38" s="25">
@@ -9078,16 +9468,16 @@
         <v>1750000</v>
       </c>
       <c r="I38" s="71">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38" s="53">
         <f t="shared" si="0"/>
-        <v>3500000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="248"/>
-      <c r="B39" s="132" t="s">
+      <c r="A39" s="244"/>
+      <c r="B39" s="131" t="s">
         <v>142</v>
       </c>
       <c r="C39" s="27">
@@ -9102,70 +9492,70 @@
       <c r="F39" s="28">
         <v>2114</v>
       </c>
-      <c r="G39" s="124">
+      <c r="G39" s="123">
         <v>1284</v>
       </c>
       <c r="H39" s="55">
         <v>3200000</v>
       </c>
       <c r="I39" s="72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J39" s="55">
         <f t="shared" si="0"/>
-        <v>6400000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="134" t="s">
+      <c r="A40" s="133" t="s">
         <v>145</v>
       </c>
-      <c r="B40" s="135" t="s">
+      <c r="B40" s="134" t="s">
         <v>140</v>
       </c>
       <c r="C40" s="7">
         <v>4</v>
       </c>
-      <c r="D40" s="133">
+      <c r="D40" s="132">
         <v>15</v>
       </c>
-      <c r="E40" s="133">
+      <c r="E40" s="132">
         <v>46</v>
       </c>
-      <c r="F40" s="136">
+      <c r="F40" s="135">
         <v>1919</v>
       </c>
       <c r="G40" s="13">
         <v>1285</v>
       </c>
-      <c r="H40" s="137">
+      <c r="H40" s="136">
         <v>250000</v>
       </c>
       <c r="I40" s="109"/>
-      <c r="J40" s="138">
+      <c r="J40" s="137">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H41" s="234" t="s">
+      <c r="H41" s="230" t="s">
         <v>43</v>
       </c>
-      <c r="I41" s="235"/>
-      <c r="J41" s="219">
+      <c r="I41" s="231"/>
+      <c r="J41" s="217">
         <f>SUM(J2:J40)</f>
-        <v>31130000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H42" s="217"/>
-      <c r="I42" s="236"/>
-      <c r="J42" s="220"/>
+      <c r="H42" s="215"/>
+      <c r="I42" s="232"/>
+      <c r="J42" s="218"/>
     </row>
     <row r="44" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B45" s="162" t="s">
-        <v>209</v>
+      <c r="B45" s="161" t="s">
+        <v>208</v>
       </c>
       <c r="C45" s="23">
         <v>4</v>
@@ -9184,8 +9574,8 @@
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B46" s="159" t="s">
-        <v>210</v>
+      <c r="B46" s="158" t="s">
+        <v>209</v>
       </c>
       <c r="C46" s="25">
         <v>4</v>
@@ -9204,8 +9594,8 @@
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B47" s="159" t="s">
-        <v>211</v>
+      <c r="B47" s="158" t="s">
+        <v>210</v>
       </c>
       <c r="C47" s="25">
         <v>4</v>
@@ -9224,8 +9614,8 @@
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B48" s="159" t="s">
-        <v>213</v>
+      <c r="B48" s="158" t="s">
+        <v>212</v>
       </c>
       <c r="C48" s="25">
         <v>4</v>
@@ -9244,8 +9634,8 @@
       </c>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B49" s="159" t="s">
-        <v>212</v>
+      <c r="B49" s="158" t="s">
+        <v>211</v>
       </c>
       <c r="C49" s="25">
         <v>4</v>
@@ -9264,8 +9654,8 @@
       </c>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B50" s="159" t="s">
-        <v>214</v>
+      <c r="B50" s="158" t="s">
+        <v>213</v>
       </c>
       <c r="C50" s="25">
         <v>4</v>
@@ -9284,8 +9674,8 @@
       </c>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B51" s="159" t="s">
-        <v>214</v>
+      <c r="B51" s="158" t="s">
+        <v>213</v>
       </c>
       <c r="C51" s="25">
         <v>4</v>
@@ -9304,8 +9694,8 @@
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B52" s="159" t="s">
-        <v>214</v>
+      <c r="B52" s="158" t="s">
+        <v>213</v>
       </c>
       <c r="C52" s="25">
         <v>4</v>
@@ -9322,11 +9712,11 @@
       <c r="G52" s="36">
         <v>1305</v>
       </c>
-      <c r="H52" s="161"/>
+      <c r="H52" s="160"/>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B53" s="159" t="s">
-        <v>215</v>
+      <c r="B53" s="158" t="s">
+        <v>214</v>
       </c>
       <c r="C53" s="25">
         <v>4</v>
@@ -9343,11 +9733,11 @@
       <c r="G53" s="36">
         <v>1306</v>
       </c>
-      <c r="I53" s="122"/>
+      <c r="I53" s="121"/>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B54" s="159" t="s">
-        <v>216</v>
+      <c r="B54" s="158" t="s">
+        <v>215</v>
       </c>
       <c r="C54" s="25">
         <v>4</v>
@@ -9366,8 +9756,8 @@
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B55" s="159" t="s">
-        <v>217</v>
+      <c r="B55" s="158" t="s">
+        <v>216</v>
       </c>
       <c r="C55" s="25">
         <v>4</v>
@@ -9386,8 +9776,8 @@
       </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B56" s="159" t="s">
-        <v>218</v>
+      <c r="B56" s="158" t="s">
+        <v>217</v>
       </c>
       <c r="C56" s="25">
         <v>4</v>
@@ -9404,12 +9794,12 @@
       <c r="G56" s="36">
         <v>1309</v>
       </c>
-      <c r="H56" s="161"/>
-      <c r="I56" s="122"/>
+      <c r="H56" s="160"/>
+      <c r="I56" s="121"/>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B57" s="159" t="s">
-        <v>219</v>
+      <c r="B57" s="158" t="s">
+        <v>218</v>
       </c>
       <c r="C57" s="25">
         <v>4</v>
@@ -9428,8 +9818,8 @@
       </c>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B58" s="159" t="s">
-        <v>220</v>
+      <c r="B58" s="158" t="s">
+        <v>219</v>
       </c>
       <c r="C58" s="25">
         <v>4</v>
@@ -9446,11 +9836,11 @@
       <c r="G58" s="36">
         <v>1311</v>
       </c>
-      <c r="H58" s="161"/>
+      <c r="H58" s="160"/>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B59" s="159" t="s">
-        <v>221</v>
+      <c r="B59" s="158" t="s">
+        <v>220</v>
       </c>
       <c r="C59" s="25">
         <v>4</v>
@@ -9467,11 +9857,11 @@
       <c r="G59" s="36">
         <v>1312</v>
       </c>
-      <c r="I59" s="122"/>
+      <c r="I59" s="121"/>
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B60" s="159" t="s">
-        <v>222</v>
+      <c r="B60" s="158" t="s">
+        <v>221</v>
       </c>
       <c r="C60" s="25">
         <v>4</v>
@@ -9490,8 +9880,8 @@
       </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B61" s="159" t="s">
-        <v>223</v>
+      <c r="B61" s="158" t="s">
+        <v>222</v>
       </c>
       <c r="C61" s="25">
         <v>4</v>
@@ -9508,11 +9898,11 @@
       <c r="G61" s="36">
         <v>1314</v>
       </c>
-      <c r="I61" s="122"/>
+      <c r="I61" s="121"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B62" s="159" t="s">
-        <v>224</v>
+      <c r="B62" s="158" t="s">
+        <v>223</v>
       </c>
       <c r="C62" s="25">
         <v>4</v>
@@ -9531,8 +9921,8 @@
       </c>
     </row>
     <row r="63" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="160" t="s">
-        <v>225</v>
+      <c r="B63" s="159" t="s">
+        <v>224</v>
       </c>
       <c r="C63" s="27">
         <v>4</v>
@@ -9570,21 +9960,21 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="57.140625" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" style="191" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" style="186" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" style="1"/>
     <col min="5" max="5" width="21.28515625" style="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="109"/>
-      <c r="C1" s="196" t="s">
+      <c r="C1" s="183" t="s">
         <v>103</v>
       </c>
       <c r="D1" s="13" t="s">
@@ -9594,540 +9984,564 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="107" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="249" t="s">
+      <c r="B2" s="219" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="187">
+      <c r="C2" s="301">
         <f>+AA!I2</f>
         <v>25000</v>
       </c>
-      <c r="D2" s="42">
+      <c r="D2" s="302">
         <v>20</v>
       </c>
-      <c r="E2" s="251">
-        <f>+(C2*D2)+(C3*D3)</f>
-        <v>820000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="108" t="s">
+      <c r="E2" s="247">
+        <v>1360000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="300" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="286" t="s">
+        <v>249</v>
+      </c>
+      <c r="B3" s="245"/>
+      <c r="C3" s="304">
+        <v>28000</v>
+      </c>
+      <c r="D3" s="303">
+        <v>20</v>
+      </c>
+      <c r="E3" s="251"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="108" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="250"/>
-      <c r="C3" s="187">
+      <c r="B4" s="246"/>
+      <c r="C4" s="298">
         <f>+AA!I4</f>
         <v>32000</v>
       </c>
-      <c r="D3" s="37">
+      <c r="D4" s="287">
         <v>10</v>
       </c>
-      <c r="E3" s="252"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="107" t="s">
+      <c r="E4" s="248"/>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="107" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="249" t="s">
+      <c r="B5" s="219" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="188">
+      <c r="C5" s="305">
         <f>+AA!I8</f>
         <v>120000</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D5" s="35">
         <v>20</v>
       </c>
-      <c r="E4" s="251">
-        <f>+(C4*D4)+(C5*D5)</f>
-        <v>3700000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="108" t="s">
+      <c r="E5" s="255">
+        <v>4800000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="286" t="s">
+        <v>250</v>
+      </c>
+      <c r="B6" s="245"/>
+      <c r="C6" s="306">
+        <v>110000</v>
+      </c>
+      <c r="D6" s="36">
+        <v>10</v>
+      </c>
+      <c r="E6" s="256"/>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="108" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="250"/>
-      <c r="C5" s="189">
+      <c r="B7" s="246"/>
+      <c r="C7" s="307">
         <f>+AA!I9</f>
         <v>130000</v>
       </c>
-      <c r="D5" s="38">
+      <c r="D7" s="38">
         <v>10</v>
       </c>
-      <c r="E5" s="252"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="107" t="s">
+      <c r="E7" s="308"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="107" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="249" t="s">
+      <c r="B8" s="249" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="188">
+      <c r="C8" s="182">
         <f>+AA!I6</f>
         <v>110000</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D8" s="42">
         <v>20</v>
       </c>
-      <c r="E6" s="251">
-        <f>+(C6*D6)+(C7*D7)</f>
+      <c r="E8" s="247">
+        <f>+(C8*D8)+(C9*D9)</f>
         <v>3350000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="108" t="s">
+    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="108" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="250"/>
-      <c r="C7" s="187">
+      <c r="B9" s="250"/>
+      <c r="C9" s="182">
         <f>+AA!I7</f>
         <v>115000</v>
       </c>
-      <c r="D7" s="37">
+      <c r="D9" s="37">
         <v>10</v>
       </c>
-      <c r="E7" s="252"/>
-    </row>
-    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="63" t="s">
+      <c r="E9" s="248"/>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="143" t="s">
+      <c r="B10" s="142" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="91">
+      <c r="C10" s="309">
         <v>325000</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D10" s="13">
         <v>10</v>
       </c>
-      <c r="E8" s="283">
-        <f t="shared" ref="E8" si="0">C8*D8</f>
+      <c r="E10" s="198">
+        <f t="shared" ref="E10" si="0">C10*D10</f>
         <v>3250000</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="111" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="111" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="249" t="s">
+      <c r="B11" s="219" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="188">
+      <c r="C11" s="301">
         <f>+AA!I29</f>
         <v>27000</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D11" s="87">
         <v>20</v>
       </c>
-      <c r="E9" s="251">
-        <f>+(C9*D9)+(C10*D10)</f>
+      <c r="E11" s="247">
+        <f>+(C11*D11)+(C12*D12)</f>
         <v>1690000</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="112" t="s">
+    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="112" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="250"/>
-      <c r="C10" s="187">
+      <c r="B12" s="246"/>
+      <c r="C12" s="298">
         <f>+AA!I39</f>
         <v>115000</v>
       </c>
-      <c r="D10" s="37">
+      <c r="D12" s="287">
         <v>10</v>
       </c>
-      <c r="E10" s="252"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="113" t="s">
+      <c r="E12" s="248"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="113" t="s">
         <v>81</v>
       </c>
-      <c r="B11" s="221" t="s">
+      <c r="B13" s="219" t="s">
         <v>102</v>
       </c>
-      <c r="C11" s="193">
+      <c r="C13" s="187">
         <f>+AA!I47</f>
         <v>76000</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D13" s="15">
         <v>20</v>
       </c>
-      <c r="E11" s="251">
-        <f>+(C11*D11)+(C12*D12)</f>
+      <c r="E13" s="247">
+        <f>+(C13*D13)+(C14*D14)</f>
         <v>2320000</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="106" t="s">
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="106" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="253"/>
-      <c r="C12" s="192">
+      <c r="B14" s="245"/>
+      <c r="C14" s="187">
         <f>+AA!I44</f>
         <v>80000</v>
       </c>
-      <c r="D12" s="143">
+      <c r="D14" s="142">
         <v>10</v>
       </c>
-      <c r="E12" s="256"/>
-    </row>
-    <row r="13" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="282" t="s">
-        <v>245</v>
-      </c>
-      <c r="B13" s="254"/>
-      <c r="C13" s="194">
+      <c r="E14" s="251"/>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="197" t="s">
+        <v>244</v>
+      </c>
+      <c r="B15" s="246"/>
+      <c r="C15" s="189">
         <v>110000</v>
       </c>
-      <c r="D13" s="124">
+      <c r="D15" s="123">
         <v>10</v>
       </c>
-      <c r="E13" s="252"/>
-      <c r="G13" s="284"/>
-    </row>
-    <row r="14" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="15" t="s">
+      <c r="E15" s="248"/>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C14" s="187">
+      <c r="C16" s="182">
         <f>+AA!I41</f>
         <v>85000</v>
       </c>
-      <c r="D14" s="143">
+      <c r="D16" s="142">
         <v>30</v>
       </c>
-      <c r="E14" s="77">
-        <f>+C14*D14</f>
+      <c r="E16" s="77">
+        <f>+C16*D16</f>
         <v>2550000</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="119" t="s">
+    <row r="17" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="297" t="s">
         <v>98</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B17" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="190">
+      <c r="C17" s="189">
         <f>+AA!I51</f>
         <v>55000</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D17" s="123">
         <v>30</v>
       </c>
-      <c r="E15" s="43">
-        <f>+C15*D15</f>
+      <c r="E17" s="195">
+        <f>+C17*D17</f>
         <v>1650000</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="120" t="s">
+    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="119" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B18" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="190">
+      <c r="C18" s="185">
         <f>+AA!I52</f>
         <v>75000</v>
       </c>
-      <c r="D16" s="13">
+      <c r="D18" s="13">
         <v>30</v>
       </c>
-      <c r="E16" s="43">
-        <f>+C16*D16</f>
+      <c r="E18" s="43">
+        <f>+C18*D18</f>
         <v>2250000</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="121" t="s">
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="120" t="s">
         <v>101</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B19" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="C17" s="190">
+      <c r="C19" s="185">
         <f>+AA!I53</f>
         <v>65000</v>
       </c>
-      <c r="D17" s="13">
+      <c r="D19" s="13">
         <v>30</v>
       </c>
-      <c r="E17" s="43">
-        <f>+C17*D17</f>
+      <c r="E19" s="43">
+        <f>+C19*D19</f>
         <v>1950000</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" s="109"/>
-      <c r="C19" s="186"/>
-      <c r="D19" s="13" t="s">
+    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" s="109"/>
+      <c r="C21" s="181"/>
+      <c r="D21" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="43" t="s">
+      <c r="E21" s="43" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="107" t="s">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="107" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="253" t="s">
+      <c r="B22" s="245" t="s">
         <v>102</v>
       </c>
-      <c r="C20" s="192">
+      <c r="C22" s="187">
         <f>+AA!I16</f>
         <v>175000</v>
       </c>
-      <c r="D20" s="42">
+      <c r="D22" s="42">
         <v>10</v>
       </c>
-      <c r="E20" s="251">
-        <f>+(C20*D20)+(C21*D21)</f>
+      <c r="E22" s="247">
+        <f>+(C22*D22)+(C23*D23)</f>
         <v>5750000</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="108" t="s">
+      <c r="G22" s="121"/>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="254"/>
-      <c r="C21" s="192">
+      <c r="B23" s="246"/>
+      <c r="C23" s="187">
         <f>+AA!I18</f>
         <v>200000</v>
       </c>
-      <c r="D21" s="37">
+      <c r="D23" s="37">
         <v>20</v>
       </c>
-      <c r="E21" s="252"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="111" t="s">
+      <c r="E23" s="248"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="111" t="s">
         <v>71</v>
       </c>
-      <c r="B22" s="221" t="s">
+      <c r="B24" s="219" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="193">
+      <c r="C24" s="188">
         <f>+AA!I37</f>
         <v>130000</v>
       </c>
-      <c r="D22" s="35">
+      <c r="D24" s="35">
         <v>20</v>
       </c>
-      <c r="E22" s="251">
-        <f>+(C22*D22)+(C23*D23)</f>
+      <c r="E24" s="247">
+        <f>+(C24*D24)+(C25*D25)</f>
         <v>3850000</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="154" t="s">
+    <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="153" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="254"/>
-      <c r="C23" s="194">
+      <c r="B25" s="246"/>
+      <c r="C25" s="189">
         <f>+AA!I36</f>
         <v>125000</v>
       </c>
-      <c r="D23" s="38">
+      <c r="D25" s="38">
         <v>10</v>
       </c>
-      <c r="E23" s="252"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="113" t="s">
+      <c r="E25" s="248"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="113" t="s">
         <v>79</v>
       </c>
-      <c r="B24" s="249" t="s">
+      <c r="B26" s="249" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="188">
+      <c r="C26" s="183">
         <f>+AA!I45</f>
         <v>260000</v>
       </c>
-      <c r="D24" s="35">
+      <c r="D26" s="35">
         <v>20</v>
       </c>
-      <c r="E24" s="251">
-        <f>+(C24*D24)+(C25*D25)</f>
+      <c r="E26" s="247">
+        <f>+(C26*D26)+(C27*D27)</f>
         <v>6340000</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="106" t="s">
+    <row r="27" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="106" t="s">
         <v>84</v>
       </c>
-      <c r="B25" s="250"/>
-      <c r="C25" s="189">
+      <c r="B27" s="250"/>
+      <c r="C27" s="184">
         <f>+AA!I50</f>
         <v>114000</v>
       </c>
-      <c r="D25" s="38">
+      <c r="D27" s="38">
         <v>10</v>
       </c>
-      <c r="E25" s="252"/>
-    </row>
-    <row r="26" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="5"/>
-      <c r="B26" s="115"/>
-      <c r="C26" s="195"/>
-      <c r="E26" s="116"/>
-    </row>
-    <row r="27" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="12" t="s">
+      <c r="E27" s="248"/>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="5"/>
+      <c r="B28" s="115"/>
+      <c r="C28" s="190"/>
+      <c r="E28" s="116"/>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="109"/>
-      <c r="C27" s="186"/>
-      <c r="D27" s="13" t="s">
+      <c r="B29" s="109"/>
+      <c r="C29" s="181"/>
+      <c r="D29" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="43" t="s">
+      <c r="E29" s="43" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="107" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="107" t="s">
         <v>50</v>
       </c>
-      <c r="B28" s="253" t="s">
+      <c r="B30" s="245" t="s">
         <v>102</v>
       </c>
-      <c r="C28" s="192">
+      <c r="C30" s="187">
         <f>+AA!I19</f>
         <v>289000</v>
       </c>
-      <c r="D28" s="42">
+      <c r="D30" s="42">
         <v>10</v>
       </c>
-      <c r="E28" s="251">
-        <f>+(C28*D28)+(C29*D29)</f>
+      <c r="E30" s="247">
+        <f>+(C30*D30)+(C31*D31)</f>
         <v>10890000</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="108" t="s">
+    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="108" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="254"/>
-      <c r="C29" s="192">
+      <c r="B31" s="246"/>
+      <c r="C31" s="187">
         <f>+AA!I20</f>
         <v>400000</v>
       </c>
-      <c r="D29" s="37">
+      <c r="D31" s="37">
         <v>20</v>
       </c>
-      <c r="E29" s="252"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="107" t="s">
+      <c r="E31" s="248"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="107" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="253" t="s">
+      <c r="B32" s="245" t="s">
         <v>102</v>
       </c>
-      <c r="C30" s="192">
+      <c r="C32" s="187">
         <f>+AA!I21</f>
         <v>700000</v>
       </c>
-      <c r="D30" s="35">
+      <c r="D32" s="35">
         <v>5</v>
       </c>
-      <c r="E30" s="251">
-        <f>+(C30*D30)+(C31*D31)</f>
+      <c r="E32" s="247">
+        <f>+(C32*D32)+(C33*D33)</f>
         <v>20300000</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="108" t="s">
+    <row r="33" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="108" t="s">
         <v>96</v>
       </c>
-      <c r="B31" s="254"/>
-      <c r="C31" s="194">
+      <c r="B33" s="246"/>
+      <c r="C33" s="189">
         <f>+AA!I24</f>
         <v>1120000</v>
       </c>
-      <c r="D31" s="38">
+      <c r="D33" s="38">
         <v>15</v>
       </c>
-      <c r="E31" s="252"/>
-    </row>
-    <row r="32" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="114" t="s">
+      <c r="E33" s="248"/>
+    </row>
+    <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="114" t="s">
         <v>76</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B34" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="C32" s="196">
+      <c r="C34" s="191">
         <f>+AA!I42</f>
         <v>400000</v>
       </c>
-      <c r="D32" s="13">
+      <c r="D34" s="13">
         <v>25</v>
       </c>
-      <c r="E32" s="43">
-        <f>+C32*D32</f>
+      <c r="E34" s="43">
+        <f>+C34*D34</f>
         <v>10000000</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="20" t="s">
+    <row r="35" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B35" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="C33" s="196">
+      <c r="C35" s="191">
         <f>+AA!I40</f>
         <v>200000</v>
       </c>
-      <c r="D33" s="13">
+      <c r="D35" s="13">
         <v>30</v>
       </c>
-      <c r="E33" s="43">
-        <f>+C33*D33</f>
+      <c r="E35" s="43">
+        <f>+C35*D35</f>
         <v>6000000</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="I34" s="122"/>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I36" s="121"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="E24:E25"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="E26:E27"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="E30:E31"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="E24:E25"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="E6:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -10139,7 +10553,7 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="80.28515625" customWidth="1"/>
@@ -10149,7 +10563,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B1" s="109"/>
       <c r="C1" s="15" t="s">
@@ -10160,8 +10574,8 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="286" t="s">
-        <v>246</v>
+      <c r="A2" s="200" t="s">
+        <v>245</v>
       </c>
       <c r="B2" s="249" t="s">
         <v>102</v>
@@ -10169,37 +10583,37 @@
       <c r="C2" s="14">
         <v>10</v>
       </c>
-      <c r="D2" s="251">
+      <c r="D2" s="247">
         <v>2000000</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="286" t="s">
-        <v>247</v>
+      <c r="A3" s="200" t="s">
+        <v>246</v>
       </c>
       <c r="B3" s="250"/>
-      <c r="C3" s="197">
+      <c r="C3" s="192">
         <v>5</v>
       </c>
-      <c r="D3" s="252"/>
+      <c r="D3" s="248"/>
     </row>
     <row r="4" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="285" t="s">
+      <c r="A4" s="199" t="s">
         <v>158</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C4" s="124">
+      <c r="C4" s="123">
         <v>40</v>
       </c>
-      <c r="D4" s="198">
+      <c r="D4" s="193">
         <v>480000</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="107" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B5" s="249" t="s">
         <v>102</v>
@@ -10207,19 +10621,19 @@
       <c r="C5" s="42">
         <v>20</v>
       </c>
-      <c r="D5" s="251">
+      <c r="D5" s="247">
         <v>44000</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="105" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B6" s="250"/>
       <c r="C6" s="37">
         <v>20</v>
       </c>
-      <c r="D6" s="252"/>
+      <c r="D6" s="248"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="107" t="s">
@@ -10231,19 +10645,19 @@
       <c r="C7" s="35">
         <v>20</v>
       </c>
-      <c r="D7" s="251">
+      <c r="D7" s="247">
         <v>617000</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="156" t="s">
+      <c r="A8" s="155" t="s">
         <v>154</v>
       </c>
-      <c r="B8" s="255"/>
-      <c r="C8" s="143">
-        <v>4</v>
-      </c>
-      <c r="D8" s="256"/>
+      <c r="B8" s="252"/>
+      <c r="C8" s="142">
+        <v>4</v>
+      </c>
+      <c r="D8" s="251"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="108" t="s">
@@ -10253,11 +10667,11 @@
       <c r="C9" s="38">
         <v>2</v>
       </c>
-      <c r="D9" s="252"/>
+      <c r="D9" s="248"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="107" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B10" s="249" t="s">
         <v>102</v>
@@ -10265,19 +10679,19 @@
       <c r="C10" s="35">
         <v>20</v>
       </c>
-      <c r="D10" s="251">
+      <c r="D10" s="247">
         <v>1040000</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="156" t="s">
+      <c r="A11" s="155" t="s">
         <v>156</v>
       </c>
-      <c r="B11" s="255"/>
-      <c r="C11" s="143">
-        <v>4</v>
-      </c>
-      <c r="D11" s="256"/>
+      <c r="B11" s="252"/>
+      <c r="C11" s="142">
+        <v>4</v>
+      </c>
+      <c r="D11" s="251"/>
     </row>
     <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="108" t="s">
@@ -10287,134 +10701,134 @@
       <c r="C12" s="37">
         <v>2</v>
       </c>
-      <c r="D12" s="252"/>
+      <c r="D12" s="248"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="107" t="s">
-        <v>160</v>
+      <c r="A13" s="111" t="s">
+        <v>184</v>
       </c>
       <c r="B13" s="249" t="s">
         <v>102</v>
       </c>
       <c r="C13" s="35">
-        <v>4</v>
-      </c>
-      <c r="D13" s="251">
-        <v>6800000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="157" t="s">
-        <v>161</v>
-      </c>
-      <c r="B14" s="255"/>
-      <c r="C14" s="143">
+        <v>20</v>
+      </c>
+      <c r="D13" s="247">
+        <v>260000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="163" t="s">
+        <v>185</v>
+      </c>
+      <c r="B14" s="252"/>
+      <c r="C14" s="142">
+        <v>20</v>
+      </c>
+      <c r="D14" s="251"/>
+      <c r="F14" s="121"/>
+    </row>
+    <row r="15" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="112" t="s">
+        <v>186</v>
+      </c>
+      <c r="B15" s="250"/>
+      <c r="C15" s="37">
+        <v>10</v>
+      </c>
+      <c r="D15" s="248"/>
+    </row>
+    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="113" t="s">
+        <v>231</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="35">
+        <v>20</v>
+      </c>
+      <c r="D16" s="77">
+        <v>40000</v>
+      </c>
+      <c r="F16" s="121"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="154" t="s">
+        <v>199</v>
+      </c>
+      <c r="B17" s="249" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" s="35">
+        <v>4</v>
+      </c>
+      <c r="D17" s="247">
+        <v>2680000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="164" t="s">
+        <v>232</v>
+      </c>
+      <c r="B18" s="252"/>
+      <c r="C18" s="142">
         <v>2</v>
       </c>
-      <c r="D14" s="256"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="111" t="s">
-        <v>184</v>
-      </c>
-      <c r="B15" s="249" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" s="35">
-        <v>20</v>
-      </c>
-      <c r="D15" s="251">
-        <v>260000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="164" t="s">
-        <v>185</v>
-      </c>
-      <c r="B16" s="255"/>
-      <c r="C16" s="143">
-        <v>20</v>
-      </c>
-      <c r="D16" s="256"/>
-      <c r="F16" s="122"/>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="112" t="s">
-        <v>186</v>
-      </c>
-      <c r="B17" s="250"/>
-      <c r="C17" s="37">
-        <v>10</v>
-      </c>
-      <c r="D17" s="252"/>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="113" t="s">
-        <v>232</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="C18" s="35">
-        <v>20</v>
-      </c>
-      <c r="D18" s="77">
-        <v>40000</v>
-      </c>
-      <c r="F18" s="122"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="155" t="s">
-        <v>200</v>
+      <c r="D18" s="251"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="154" t="s">
+        <v>175</v>
       </c>
       <c r="B19" s="249" t="s">
         <v>102</v>
       </c>
       <c r="C19" s="35">
-        <v>4</v>
-      </c>
-      <c r="D19" s="251">
-        <v>2680000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="165" t="s">
-        <v>233</v>
-      </c>
-      <c r="B20" s="255"/>
-      <c r="C20" s="143">
-        <v>2</v>
-      </c>
-      <c r="D20" s="256"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="155" t="s">
-        <v>175</v>
+        <v>20</v>
+      </c>
+      <c r="D19" s="247">
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="164" t="s">
+        <v>174</v>
+      </c>
+      <c r="B20" s="252"/>
+      <c r="C20" s="142">
+        <v>10</v>
+      </c>
+      <c r="D20" s="251"/>
+    </row>
+    <row r="21" spans="1:4" s="300" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="284" t="s">
+        <v>253</v>
       </c>
       <c r="B21" s="249" t="s">
         <v>102</v>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="299">
         <v>20</v>
       </c>
-      <c r="D21" s="251">
-        <v>1800000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="167" t="s">
-        <v>174</v>
+      <c r="D21" s="247">
+        <v>208000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="300" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="285" t="s">
+        <v>254</v>
       </c>
       <c r="B22" s="250"/>
-      <c r="C22" s="124">
-        <v>10</v>
-      </c>
-      <c r="D22" s="252"/>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="315">
+        <v>20</v>
+      </c>
+      <c r="D22" s="248"/>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B24" s="109"/>
       <c r="C24" s="13" t="s">
@@ -10424,461 +10838,516 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="107" t="s">
         <v>162</v>
       </c>
-      <c r="B25" s="253" t="s">
+      <c r="B25" s="245" t="s">
         <v>102</v>
       </c>
       <c r="C25" s="42">
         <v>4</v>
       </c>
-      <c r="D25" s="251">
+      <c r="D25" s="247">
         <v>10500000</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="108" t="s">
         <v>163</v>
       </c>
-      <c r="B26" s="254"/>
+      <c r="B26" s="246"/>
       <c r="C26" s="37">
         <v>1</v>
       </c>
-      <c r="D26" s="252"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="111" t="s">
-        <v>227</v>
-      </c>
-      <c r="B27" s="221" t="s">
+      <c r="D26" s="248"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="107" t="s">
+        <v>160</v>
+      </c>
+      <c r="B27" s="249" t="s">
         <v>102</v>
       </c>
       <c r="C27" s="35">
         <v>4</v>
       </c>
-      <c r="D27" s="251">
+      <c r="D27" s="247">
+        <v>6800000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="156" t="s">
+        <v>161</v>
+      </c>
+      <c r="B28" s="252"/>
+      <c r="C28" s="142">
+        <v>2</v>
+      </c>
+      <c r="D28" s="251"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="111" t="s">
+        <v>226</v>
+      </c>
+      <c r="B29" s="219" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="35">
+        <v>4</v>
+      </c>
+      <c r="D29" s="247">
         <v>2900000</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="112" t="s">
+    <row r="30" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="112" t="s">
         <v>195</v>
       </c>
-      <c r="B28" s="254"/>
-      <c r="C28" s="38">
-        <v>2</v>
-      </c>
-      <c r="D28" s="252"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="155" t="s">
-        <v>176</v>
-      </c>
-      <c r="B29" s="249" t="s">
-        <v>102</v>
-      </c>
-      <c r="C29" s="35">
-        <v>4</v>
-      </c>
-      <c r="D29" s="251">
-        <v>4500000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="166" t="s">
-        <v>177</v>
-      </c>
-      <c r="B30" s="250"/>
+      <c r="B30" s="246"/>
       <c r="C30" s="38">
         <v>2</v>
       </c>
-      <c r="D30" s="252"/>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="5"/>
-      <c r="B31" s="115"/>
-      <c r="D31" s="116"/>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="B32" s="109"/>
-      <c r="C32" s="13" t="s">
+      <c r="D30" s="248"/>
+    </row>
+    <row r="31" spans="1:4" s="300" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="285" t="s">
+        <v>255</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="315">
+        <v>4</v>
+      </c>
+      <c r="D31" s="193">
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" s="300" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="285" t="s">
+        <v>256</v>
+      </c>
+      <c r="B32" s="196" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" s="318">
+        <v>2</v>
+      </c>
+      <c r="D32" s="193">
+        <v>2200000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="154" t="s">
+        <v>176</v>
+      </c>
+      <c r="B33" s="249" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" s="35">
+        <v>4</v>
+      </c>
+      <c r="D33" s="247">
+        <v>4500000</v>
+      </c>
+      <c r="F33" s="316"/>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="165" t="s">
+        <v>177</v>
+      </c>
+      <c r="B34" s="250"/>
+      <c r="C34" s="38">
+        <v>2</v>
+      </c>
+      <c r="D34" s="248"/>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="5"/>
+      <c r="B35" s="115"/>
+      <c r="D35" s="116"/>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="B36" s="109"/>
+      <c r="C36" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="43" t="s">
+      <c r="D36" s="43" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="120" t="s">
+    <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="119" t="s">
         <v>164</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C33" s="42">
-        <v>10</v>
-      </c>
-      <c r="D33" s="43">
-        <v>3500000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="120" t="s">
-        <v>168</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C34" s="37">
-        <v>10</v>
-      </c>
-      <c r="D34" s="168">
-        <v>800000</v>
-      </c>
-      <c r="G34" s="122"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="153" t="s">
-        <v>193</v>
-      </c>
-      <c r="B35" s="253" t="s">
-        <v>102</v>
-      </c>
-      <c r="C35" s="35">
-        <v>2</v>
-      </c>
-      <c r="D35" s="251">
-        <v>5600000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="154" t="s">
-        <v>194</v>
-      </c>
-      <c r="B36" s="254"/>
-      <c r="C36" s="38">
-        <v>6</v>
-      </c>
-      <c r="D36" s="252"/>
-    </row>
-    <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="114" t="s">
-        <v>199</v>
       </c>
       <c r="B37" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="C37" s="13">
-        <v>4</v>
+      <c r="C37" s="42">
+        <v>10</v>
       </c>
       <c r="D37" s="43">
+        <v>3500000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="119" t="s">
+        <v>168</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C38" s="37">
+        <v>10</v>
+      </c>
+      <c r="D38" s="166">
+        <v>800000</v>
+      </c>
+      <c r="G38" s="121"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="152" t="s">
+        <v>193</v>
+      </c>
+      <c r="B39" s="245" t="s">
+        <v>102</v>
+      </c>
+      <c r="C39" s="35">
+        <v>2</v>
+      </c>
+      <c r="D39" s="247">
+        <v>5600000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="153" t="s">
+        <v>194</v>
+      </c>
+      <c r="B40" s="246"/>
+      <c r="C40" s="38">
+        <v>6</v>
+      </c>
+      <c r="D40" s="248"/>
+    </row>
+    <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="114" t="s">
+        <v>198</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C41" s="13">
+        <v>4</v>
+      </c>
+      <c r="D41" s="43">
         <v>2400000</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H38" s="122"/>
-    </row>
-    <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="14" t="s">
+    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H42" s="121"/>
+    </row>
+    <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="B43" s="109"/>
+      <c r="C43" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43" s="43" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="107" t="s">
+        <v>166</v>
+      </c>
+      <c r="B44" s="221" t="s">
+        <v>102</v>
+      </c>
+      <c r="C44" s="35">
+        <v>6</v>
+      </c>
+      <c r="D44" s="247">
+        <v>2220000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="108" t="s">
+        <v>167</v>
+      </c>
+      <c r="B45" s="253"/>
+      <c r="C45" s="38">
+        <v>6</v>
+      </c>
+      <c r="D45" s="248"/>
+      <c r="G45" s="121"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="107" t="s">
+        <v>206</v>
+      </c>
+      <c r="B46" s="221" t="s">
+        <v>102</v>
+      </c>
+      <c r="C46" s="35">
+        <v>20</v>
+      </c>
+      <c r="D46" s="247">
+        <v>4250000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="108" t="s">
+        <v>207</v>
+      </c>
+      <c r="B47" s="253"/>
+      <c r="C47" s="38">
+        <v>10</v>
+      </c>
+      <c r="D47" s="248"/>
+      <c r="G47" s="121"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="151" t="s">
+        <v>227</v>
+      </c>
+      <c r="B48" s="245" t="s">
+        <v>102</v>
+      </c>
+      <c r="C48" s="35">
+        <v>10</v>
+      </c>
+      <c r="D48" s="247">
+        <v>4500000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="148" t="s">
+        <v>228</v>
+      </c>
+      <c r="B49" s="245"/>
+      <c r="C49" s="142">
+        <v>10</v>
+      </c>
+      <c r="D49" s="251"/>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="148" t="s">
+        <v>225</v>
+      </c>
+      <c r="B50" s="246"/>
+      <c r="C50" s="38">
+        <v>20</v>
+      </c>
+      <c r="D50" s="248"/>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="120" t="s">
+        <v>229</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="C51" s="13">
+        <v>16</v>
+      </c>
+      <c r="D51" s="43">
+        <v>2400000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="53" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="B39" s="109"/>
-      <c r="C39" s="13" t="s">
+      <c r="B53" s="109"/>
+      <c r="C53" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D39" s="43" t="s">
+      <c r="D53" s="43" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="107" t="s">
-        <v>166</v>
-      </c>
-      <c r="B40" s="223" t="s">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="107" t="s">
+        <v>169</v>
+      </c>
+      <c r="B54" s="249" t="s">
         <v>102</v>
       </c>
-      <c r="C40" s="35">
-        <v>6</v>
-      </c>
-      <c r="D40" s="251">
-        <v>2220000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="108" t="s">
-        <v>167</v>
-      </c>
-      <c r="B41" s="260"/>
-      <c r="C41" s="38">
-        <v>6</v>
-      </c>
-      <c r="D41" s="252"/>
-      <c r="G41" s="122"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="107" t="s">
-        <v>207</v>
-      </c>
-      <c r="B42" s="223" t="s">
+      <c r="C54" s="42">
+        <v>60</v>
+      </c>
+      <c r="D54" s="247">
+        <v>4260000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="108" t="s">
+        <v>170</v>
+      </c>
+      <c r="B55" s="250"/>
+      <c r="C55" s="37">
+        <v>60</v>
+      </c>
+      <c r="D55" s="248"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="107" t="s">
+        <v>171</v>
+      </c>
+      <c r="B56" s="249" t="s">
         <v>102</v>
       </c>
-      <c r="C42" s="35">
-        <v>20</v>
-      </c>
-      <c r="D42" s="251">
-        <v>4250000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="108" t="s">
-        <v>208</v>
-      </c>
-      <c r="B43" s="260"/>
-      <c r="C43" s="38">
-        <v>10</v>
-      </c>
-      <c r="D43" s="252"/>
-      <c r="G43" s="122"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="152" t="s">
-        <v>228</v>
-      </c>
-      <c r="B44" s="253" t="s">
+      <c r="C56" s="35">
+        <v>60</v>
+      </c>
+      <c r="D56" s="247">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="105" t="s">
+        <v>172</v>
+      </c>
+      <c r="B57" s="252"/>
+      <c r="C57" s="142">
+        <v>60</v>
+      </c>
+      <c r="D57" s="251"/>
+    </row>
+    <row r="58" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="167" t="s">
+        <v>173</v>
+      </c>
+      <c r="B58" s="250"/>
+      <c r="C58" s="37">
+        <v>60</v>
+      </c>
+      <c r="D58" s="248"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="148" t="s">
+        <v>187</v>
+      </c>
+      <c r="B59" s="220" t="s">
         <v>102</v>
       </c>
-      <c r="C44" s="35">
-        <v>10</v>
-      </c>
-      <c r="D44" s="251">
-        <v>4500000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="149" t="s">
-        <v>229</v>
-      </c>
-      <c r="B45" s="253"/>
-      <c r="C45" s="143">
-        <v>10</v>
-      </c>
-      <c r="D45" s="256"/>
-    </row>
-    <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="149" t="s">
-        <v>226</v>
-      </c>
-      <c r="B46" s="254"/>
-      <c r="C46" s="38">
-        <v>20</v>
-      </c>
-      <c r="D46" s="252"/>
-    </row>
-    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="121" t="s">
-        <v>230</v>
-      </c>
-      <c r="B47" s="13" t="s">
+      <c r="C59" s="35">
+        <v>60</v>
+      </c>
+      <c r="D59" s="255">
+        <v>260000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="148" t="s">
+        <v>188</v>
+      </c>
+      <c r="B60" s="254"/>
+      <c r="C60" s="36">
+        <v>60</v>
+      </c>
+      <c r="D60" s="256"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="148" t="s">
+        <v>189</v>
+      </c>
+      <c r="B61" s="254"/>
+      <c r="C61" s="36">
+        <v>60</v>
+      </c>
+      <c r="D61" s="256"/>
+    </row>
+    <row r="62" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="168" t="s">
+        <v>190</v>
+      </c>
+      <c r="B62" s="254"/>
+      <c r="C62" s="38">
+        <v>60</v>
+      </c>
+      <c r="D62" s="256"/>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="120" t="s">
+        <v>179</v>
+      </c>
+      <c r="B63" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C47" s="13">
-        <v>16</v>
-      </c>
-      <c r="D47" s="43">
-        <v>2400000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="B49" s="109"/>
-      <c r="C49" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D49" s="43" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="107" t="s">
-        <v>169</v>
-      </c>
-      <c r="B50" s="249" t="s">
+      <c r="C63" s="142">
+        <v>60</v>
+      </c>
+      <c r="D63" s="77">
+        <v>150000</v>
+      </c>
+      <c r="F63" s="121"/>
+    </row>
+    <row r="64" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="114" t="s">
+        <v>180</v>
+      </c>
+      <c r="B64" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="C50" s="42">
+      <c r="C64" s="13">
         <v>60</v>
       </c>
-      <c r="D50" s="251">
-        <v>4260000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="108" t="s">
-        <v>170</v>
-      </c>
-      <c r="B51" s="250"/>
-      <c r="C51" s="37">
-        <v>60</v>
-      </c>
-      <c r="D51" s="252"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="107" t="s">
-        <v>171</v>
-      </c>
-      <c r="B52" s="249" t="s">
-        <v>102</v>
-      </c>
-      <c r="C52" s="35">
-        <v>60</v>
-      </c>
-      <c r="D52" s="251">
-        <v>900000</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="105" t="s">
-        <v>172</v>
-      </c>
-      <c r="B53" s="255"/>
-      <c r="C53" s="143">
-        <v>60</v>
-      </c>
-      <c r="D53" s="256"/>
-    </row>
-    <row r="54" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="169" t="s">
-        <v>173</v>
-      </c>
-      <c r="B54" s="250"/>
-      <c r="C54" s="37">
-        <v>60</v>
-      </c>
-      <c r="D54" s="252"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="149" t="s">
-        <v>187</v>
-      </c>
-      <c r="B55" s="222" t="s">
-        <v>102</v>
-      </c>
-      <c r="C55" s="35">
-        <v>60</v>
-      </c>
-      <c r="D55" s="258">
-        <v>260000</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="149" t="s">
-        <v>188</v>
-      </c>
-      <c r="B56" s="257"/>
-      <c r="C56" s="36">
-        <v>60</v>
-      </c>
-      <c r="D56" s="259"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="149" t="s">
-        <v>189</v>
-      </c>
-      <c r="B57" s="257"/>
-      <c r="C57" s="36">
-        <v>60</v>
-      </c>
-      <c r="D57" s="259"/>
-    </row>
-    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="170" t="s">
-        <v>190</v>
-      </c>
-      <c r="B58" s="257"/>
-      <c r="C58" s="38">
-        <v>60</v>
-      </c>
-      <c r="D58" s="259"/>
-    </row>
-    <row r="59" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="121" t="s">
-        <v>179</v>
-      </c>
-      <c r="B59" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="C59" s="143">
-        <v>60</v>
-      </c>
-      <c r="D59" s="77">
-        <v>150000</v>
-      </c>
-      <c r="F59" s="122"/>
-    </row>
-    <row r="60" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="114" t="s">
-        <v>180</v>
-      </c>
-      <c r="B60" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C60" s="13">
-        <v>60</v>
-      </c>
-      <c r="D60" s="43">
+      <c r="D64" s="43">
         <v>2100000</v>
       </c>
-      <c r="F60" s="122"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H62" s="122"/>
+      <c r="F64" s="121"/>
+    </row>
+    <row r="66" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H66" s="121"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="38">
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="D56:D58"/>
+    <mergeCell ref="B59:B62"/>
+    <mergeCell ref="D59:D62"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="B48:B50"/>
+    <mergeCell ref="D48:D50"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="D13:D15"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="D7:D9"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="D44:D46"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="D52:D54"/>
-    <mergeCell ref="B55:B58"/>
-    <mergeCell ref="D55:D58"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -10900,30 +11369,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="172" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1" s="171" t="s">
         <v>239</v>
       </c>
-      <c r="B1" s="173" t="s">
-        <v>240</v>
-      </c>
-      <c r="C1" s="173" t="s">
+      <c r="C1" s="171" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="172" t="s">
+      <c r="D1" s="170" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="59" t="s">
-        <v>243</v>
-      </c>
-      <c r="B2" s="270" t="s">
+        <v>242</v>
+      </c>
+      <c r="B2" s="266" t="s">
         <v>146</v>
       </c>
       <c r="C2" s="35">
         <v>4</v>
       </c>
-      <c r="D2" s="273">
+      <c r="D2" s="269">
         <v>10374000</v>
       </c>
     </row>
@@ -10931,171 +11400,171 @@
       <c r="A3" s="60" t="s">
         <v>106</v>
       </c>
-      <c r="B3" s="271"/>
+      <c r="B3" s="267"/>
       <c r="C3" s="36">
         <v>10</v>
       </c>
-      <c r="D3" s="274"/>
+      <c r="D3" s="270"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="60" t="s">
         <v>107</v>
       </c>
-      <c r="B4" s="271"/>
+      <c r="B4" s="267"/>
       <c r="C4" s="36">
         <v>2</v>
       </c>
-      <c r="D4" s="274"/>
+      <c r="D4" s="270"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="128" t="s">
+      <c r="A5" s="127" t="s">
         <v>108</v>
       </c>
-      <c r="B5" s="271"/>
+      <c r="B5" s="267"/>
       <c r="C5" s="36">
         <v>2</v>
       </c>
-      <c r="D5" s="274"/>
+      <c r="D5" s="270"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="271"/>
+      <c r="B6" s="267"/>
       <c r="C6" s="36">
         <v>16</v>
       </c>
-      <c r="D6" s="274"/>
+      <c r="D6" s="270"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="60" t="s">
         <v>109</v>
       </c>
-      <c r="B7" s="271"/>
+      <c r="B7" s="267"/>
       <c r="C7" s="36">
         <v>8</v>
       </c>
-      <c r="D7" s="274"/>
+      <c r="D7" s="270"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="60" t="s">
         <v>110</v>
       </c>
-      <c r="B8" s="271"/>
+      <c r="B8" s="267"/>
       <c r="C8" s="36">
         <v>20</v>
       </c>
-      <c r="D8" s="274"/>
+      <c r="D8" s="270"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="60" t="s">
         <v>115</v>
       </c>
-      <c r="B9" s="271"/>
+      <c r="B9" s="267"/>
       <c r="C9" s="36">
         <v>20</v>
       </c>
-      <c r="D9" s="274"/>
+      <c r="D9" s="270"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="60" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="271"/>
+      <c r="B10" s="267"/>
       <c r="C10" s="36">
         <v>10</v>
       </c>
-      <c r="D10" s="274"/>
+      <c r="D10" s="270"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="60" t="s">
         <v>111</v>
       </c>
-      <c r="B11" s="271"/>
+      <c r="B11" s="267"/>
       <c r="C11" s="36">
         <v>4</v>
       </c>
-      <c r="D11" s="274"/>
+      <c r="D11" s="270"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="60" t="s">
         <v>112</v>
       </c>
-      <c r="B12" s="271"/>
+      <c r="B12" s="267"/>
       <c r="C12" s="36">
         <v>4</v>
       </c>
-      <c r="D12" s="274"/>
+      <c r="D12" s="270"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="60" t="s">
         <v>113</v>
       </c>
-      <c r="B13" s="271"/>
+      <c r="B13" s="267"/>
       <c r="C13" s="36">
         <v>4</v>
       </c>
-      <c r="D13" s="274"/>
+      <c r="D13" s="270"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="60" t="s">
         <v>114</v>
       </c>
-      <c r="B14" s="271"/>
+      <c r="B14" s="267"/>
       <c r="C14" s="36">
         <v>2</v>
       </c>
-      <c r="D14" s="274"/>
+      <c r="D14" s="270"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="60" t="s">
         <v>117</v>
       </c>
-      <c r="B15" s="271"/>
+      <c r="B15" s="267"/>
       <c r="C15" s="36">
         <v>20</v>
       </c>
-      <c r="D15" s="274"/>
+      <c r="D15" s="270"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="60" t="s">
         <v>118</v>
       </c>
-      <c r="B16" s="271"/>
+      <c r="B16" s="267"/>
       <c r="C16" s="36">
         <v>20</v>
       </c>
-      <c r="D16" s="274"/>
+      <c r="D16" s="270"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="60" t="s">
         <v>119</v>
       </c>
-      <c r="B17" s="271"/>
+      <c r="B17" s="267"/>
       <c r="C17" s="36">
         <v>6</v>
       </c>
-      <c r="D17" s="274"/>
+      <c r="D17" s="270"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="60" t="s">
         <v>120</v>
       </c>
-      <c r="B18" s="271"/>
+      <c r="B18" s="267"/>
       <c r="C18" s="36">
         <v>8</v>
       </c>
-      <c r="D18" s="274"/>
+      <c r="D18" s="270"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="61" t="s">
         <v>121</v>
       </c>
-      <c r="B19" s="272"/>
+      <c r="B19" s="268"/>
       <c r="C19" s="38">
         <v>4</v>
       </c>
-      <c r="D19" s="275"/>
+      <c r="D19" s="271"/>
     </row>
     <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
@@ -11103,16 +11572,16 @@
       <c r="D20" s="116"/>
     </row>
     <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="129" t="s">
+      <c r="A21" s="128" t="s">
         <v>124</v>
       </c>
-      <c r="B21" s="264" t="s">
+      <c r="B21" s="260" t="s">
         <v>148</v>
       </c>
       <c r="C21" s="35">
         <v>2</v>
       </c>
-      <c r="D21" s="276">
+      <c r="D21" s="272">
         <v>11700000</v>
       </c>
     </row>
@@ -11120,218 +11589,218 @@
       <c r="A22" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B22" s="265"/>
+      <c r="B22" s="261"/>
       <c r="C22" s="36">
         <v>1</v>
       </c>
-      <c r="D22" s="277"/>
+      <c r="D22" s="273"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="130" t="s">
+      <c r="A23" s="129" t="s">
         <v>132</v>
       </c>
-      <c r="B23" s="265"/>
+      <c r="B23" s="261"/>
       <c r="C23" s="36">
         <v>2</v>
       </c>
-      <c r="D23" s="277"/>
+      <c r="D23" s="273"/>
     </row>
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="130" t="s">
+      <c r="A24" s="129" t="s">
         <v>127</v>
       </c>
-      <c r="B24" s="265"/>
+      <c r="B24" s="261"/>
       <c r="C24" s="36">
         <v>1</v>
       </c>
-      <c r="D24" s="277"/>
+      <c r="D24" s="273"/>
     </row>
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="131" t="s">
+      <c r="A25" s="130" t="s">
         <v>128</v>
       </c>
-      <c r="B25" s="265"/>
+      <c r="B25" s="261"/>
       <c r="C25" s="36">
         <v>1</v>
       </c>
-      <c r="D25" s="277"/>
+      <c r="D25" s="273"/>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="B26" s="265"/>
+      <c r="B26" s="261"/>
       <c r="C26" s="37">
         <v>1</v>
       </c>
-      <c r="D26" s="277"/>
+      <c r="D26" s="273"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="60" t="s">
         <v>191</v>
       </c>
-      <c r="B27" s="265"/>
+      <c r="B27" s="261"/>
       <c r="C27" s="37">
         <v>2</v>
       </c>
-      <c r="D27" s="277"/>
+      <c r="D27" s="273"/>
     </row>
     <row r="28" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="132" t="s">
+      <c r="A28" s="131" t="s">
         <v>135</v>
       </c>
-      <c r="B28" s="266"/>
+      <c r="B28" s="262"/>
       <c r="C28" s="38">
         <v>1</v>
       </c>
-      <c r="D28" s="278"/>
+      <c r="D28" s="274"/>
     </row>
     <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H29" s="122"/>
+      <c r="H29" s="121"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="129" t="s">
+      <c r="A30" s="128" t="s">
         <v>136</v>
       </c>
-      <c r="B30" s="279" t="s">
+      <c r="B30" s="275" t="s">
         <v>149</v>
       </c>
       <c r="C30" s="35">
         <v>2</v>
       </c>
-      <c r="D30" s="261">
+      <c r="D30" s="257">
         <v>640000</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="130" t="s">
+      <c r="A31" s="129" t="s">
         <v>137</v>
       </c>
-      <c r="B31" s="280"/>
+      <c r="B31" s="276"/>
       <c r="C31" s="36">
         <v>6</v>
       </c>
-      <c r="D31" s="262"/>
+      <c r="D31" s="258"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="130" t="s">
+      <c r="A32" s="129" t="s">
         <v>131</v>
       </c>
-      <c r="B32" s="280"/>
+      <c r="B32" s="276"/>
       <c r="C32" s="36">
         <v>2</v>
       </c>
-      <c r="D32" s="262"/>
+      <c r="D32" s="258"/>
     </row>
     <row r="33" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="132" t="s">
+      <c r="A33" s="131" t="s">
         <v>138</v>
       </c>
-      <c r="B33" s="281"/>
+      <c r="B33" s="277"/>
       <c r="C33" s="38">
         <v>2</v>
       </c>
-      <c r="D33" s="263"/>
+      <c r="D33" s="259"/>
     </row>
     <row r="34" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="129" t="s">
+      <c r="A35" s="128" t="s">
         <v>126</v>
       </c>
-      <c r="B35" s="264" t="s">
+      <c r="B35" s="260" t="s">
         <v>144</v>
       </c>
       <c r="C35" s="35">
         <v>4</v>
       </c>
-      <c r="D35" s="267">
+      <c r="D35" s="263">
         <v>31130000</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="130" t="s">
+      <c r="A36" s="129" t="s">
         <v>129</v>
       </c>
-      <c r="B36" s="265"/>
+      <c r="B36" s="261"/>
       <c r="C36" s="36">
         <v>2</v>
       </c>
-      <c r="D36" s="268"/>
+      <c r="D36" s="264"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="130" t="s">
+      <c r="A37" s="129" t="s">
         <v>133</v>
       </c>
-      <c r="B37" s="265"/>
+      <c r="B37" s="261"/>
       <c r="C37" s="36">
         <v>1</v>
       </c>
-      <c r="D37" s="268"/>
+      <c r="D37" s="264"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="130" t="s">
+      <c r="A38" s="129" t="s">
         <v>134</v>
       </c>
-      <c r="B38" s="265"/>
+      <c r="B38" s="261"/>
       <c r="C38" s="36">
         <v>1</v>
       </c>
-      <c r="D38" s="268"/>
+      <c r="D38" s="264"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="130" t="s">
+      <c r="A39" s="129" t="s">
         <v>125</v>
       </c>
-      <c r="B39" s="265"/>
+      <c r="B39" s="261"/>
       <c r="C39" s="36">
         <v>2</v>
       </c>
-      <c r="D39" s="268"/>
+      <c r="D39" s="264"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="130" t="s">
+      <c r="A40" s="129" t="s">
         <v>130</v>
       </c>
-      <c r="B40" s="265"/>
+      <c r="B40" s="261"/>
       <c r="C40" s="36">
         <v>2</v>
       </c>
-      <c r="D40" s="268"/>
+      <c r="D40" s="264"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="130" t="s">
+      <c r="A41" s="129" t="s">
         <v>192</v>
       </c>
-      <c r="B41" s="265"/>
+      <c r="B41" s="261"/>
       <c r="C41" s="37">
         <v>2</v>
       </c>
-      <c r="D41" s="268"/>
+      <c r="D41" s="264"/>
     </row>
     <row r="42" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="132" t="s">
+      <c r="A42" s="131" t="s">
         <v>142</v>
       </c>
-      <c r="B42" s="266"/>
+      <c r="B42" s="262"/>
       <c r="C42" s="38">
         <v>2</v>
       </c>
-      <c r="D42" s="269"/>
+      <c r="D42" s="265"/>
     </row>
     <row r="43" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D43" s="148"/>
+      <c r="D43" s="147"/>
     </row>
     <row r="44" spans="1:4" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="289" t="s">
+      <c r="A44" s="134" t="s">
         <v>165</v>
       </c>
-      <c r="B44" s="287" t="s">
-        <v>248</v>
-      </c>
-      <c r="C44" s="288">
+      <c r="B44" s="171" t="s">
+        <v>247</v>
+      </c>
+      <c r="C44" s="13">
         <v>60</v>
       </c>
-      <c r="D44" s="290">
+      <c r="D44" s="201">
         <v>1200000</v>
       </c>
     </row>
